--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output2.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output2.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X191"/>
+  <dimension ref="A1:Y191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,45 +498,50 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>AssetID_9343_smooth</t>
+          <t>AssetID_9368_smooth</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>AssetID_12208_smooth</t>
+          <t>AssetID_9369_smooth</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>AssetID_9370_smooth</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>AssetID_9358_smooth</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>AssetID_9359_smooth</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>AssetID_9360_smooth</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>AssetID_9361_smooth</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Behavior_Cluster</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Degradation_Index</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Health_Status</t>
         </is>
@@ -591,30 +596,33 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>97.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.04</v>
+        <v>71</v>
       </c>
       <c r="R2" t="n">
+        <v>74</v>
+      </c>
+      <c r="S2" t="n">
         <v>33.2</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>38.2</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>31.2</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>51.8</v>
       </c>
-      <c r="V2" t="n">
-        <v>11</v>
-      </c>
       <c r="W2" t="n">
-        <v>0.8218850039646473</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.722797444594709</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -669,30 +677,33 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.56</v>
+        <v>71</v>
       </c>
       <c r="R3" t="n">
+        <v>74</v>
+      </c>
+      <c r="S3" t="n">
         <v>33.4</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>38</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>31</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>51.8</v>
       </c>
-      <c r="V3" t="n">
-        <v>11</v>
-      </c>
       <c r="W3" t="n">
-        <v>0.739947953274347</v>
-      </c>
-      <c r="X3" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.7259397887761085</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -747,30 +758,33 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.86</v>
+        <v>71</v>
       </c>
       <c r="R4" t="n">
+        <v>74</v>
+      </c>
+      <c r="S4" t="n">
         <v>33.2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>38.4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>52</v>
       </c>
-      <c r="V4" t="n">
-        <v>11</v>
-      </c>
       <c r="W4" t="n">
-        <v>0.5490802198851416</v>
-      </c>
-      <c r="X4" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.7521195141666668</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -825,30 +839,33 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.8</v>
+        <v>71</v>
       </c>
       <c r="R5" t="n">
+        <v>74</v>
+      </c>
+      <c r="S5" t="n">
         <v>33.2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>39</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>30.2</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>51.8</v>
       </c>
-      <c r="V5" t="n">
-        <v>11</v>
-      </c>
       <c r="W5" t="n">
-        <v>0.7768468981930219</v>
-      </c>
-      <c r="X5" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8027457750985582</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -903,32 +920,35 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>93.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.64</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
+        <v>74</v>
+      </c>
+      <c r="S6" t="n">
         <v>33.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>39.2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>29.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>50.4</v>
       </c>
-      <c r="V6" t="n">
-        <v>11</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.119503695338215</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8756286866588825</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -981,32 +1001,35 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.74</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
+        <v>74</v>
+      </c>
+      <c r="S7" t="n">
         <v>33</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>39.8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>29.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>49.6</v>
       </c>
-      <c r="V7" t="n">
-        <v>11</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.297503814921174</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9384296930768551</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1082,35 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.92</v>
+        <v>71</v>
       </c>
       <c r="R8" t="n">
+        <v>74</v>
+      </c>
+      <c r="S8" t="n">
         <v>32.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>39.8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>30.2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>49.8</v>
       </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.333841249328362</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8961609324640902</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1163,35 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.64</v>
+        <v>71</v>
       </c>
       <c r="R9" t="n">
+        <v>74</v>
+      </c>
+      <c r="S9" t="n">
         <v>32</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>39.8</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>30.6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>50.2</v>
       </c>
-      <c r="V9" t="n">
-        <v>11</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.233942519786362</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.863103597091094</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -1215,30 +1244,33 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.64</v>
+        <v>71</v>
       </c>
       <c r="R10" t="n">
+        <v>74</v>
+      </c>
+      <c r="S10" t="n">
         <v>31.6</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>39.6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>31</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>51</v>
       </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.025519089539418</v>
-      </c>
-      <c r="X10" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8100993505540556</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1293,30 +1325,33 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.22</v>
+        <v>71</v>
       </c>
       <c r="R11" t="n">
+        <v>74</v>
+      </c>
+      <c r="S11" t="n">
         <v>31.2</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>40</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>31.2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>52</v>
       </c>
-      <c r="V11" t="n">
-        <v>11</v>
-      </c>
       <c r="W11" t="n">
-        <v>0.9477749450094917</v>
-      </c>
-      <c r="X11" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7982517965156241</v>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1371,30 +1406,33 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>90.2</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.22</v>
+        <v>71</v>
       </c>
       <c r="R12" t="n">
+        <v>74</v>
+      </c>
+      <c r="S12" t="n">
         <v>32</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>40</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>31.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>52.4</v>
       </c>
-      <c r="V12" t="n">
-        <v>11</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.056294231842512</v>
-      </c>
-      <c r="X12" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.7890595893110878</v>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1449,30 +1487,33 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>90.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.04</v>
+        <v>71</v>
       </c>
       <c r="R13" t="n">
+        <v>74</v>
+      </c>
+      <c r="S13" t="n">
         <v>32.4</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>40</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>30.8</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>51.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>11</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.192403633147347</v>
-      </c>
-      <c r="X13" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.8240947482608161</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1527,32 +1568,35 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>90.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.06</v>
+        <v>71</v>
       </c>
       <c r="R14" t="n">
+        <v>74</v>
+      </c>
+      <c r="S14" t="n">
         <v>32.8</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>39.8</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>30.2</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>50.6</v>
       </c>
-      <c r="V14" t="n">
-        <v>11</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.461080708792805</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8715417060966019</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -1605,30 +1649,33 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.8</v>
+        <v>71</v>
       </c>
       <c r="R15" t="n">
+        <v>74</v>
+      </c>
+      <c r="S15" t="n">
         <v>32.8</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>39.4</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>29.8</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>49.6</v>
       </c>
-      <c r="V15" t="n">
-        <v>11</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.633856697168983</v>
-      </c>
-      <c r="X15" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.908058832202155</v>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -1683,30 +1730,33 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="n">
-        <v>19.44</v>
+        <v>71</v>
       </c>
       <c r="R16" t="n">
+        <v>74</v>
+      </c>
+      <c r="S16" t="n">
         <v>32.6</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>39</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>30.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>49.8</v>
       </c>
-      <c r="V16" t="n">
-        <v>11</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.433870707715165</v>
-      </c>
-      <c r="X16" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8422551121784149</v>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1761,30 +1811,33 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>94.2192</v>
+        <v>76</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.64</v>
+        <v>71</v>
       </c>
       <c r="R17" t="n">
+        <v>74</v>
+      </c>
+      <c r="S17" t="n">
         <v>31.8</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>38.2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>31.2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>50.2</v>
       </c>
-      <c r="V17" t="n">
-        <v>11</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.187964870753287</v>
-      </c>
-      <c r="X17" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7695742125765007</v>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1839,30 +1892,33 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>95.61920000000001</v>
+        <v>76</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.04</v>
+        <v>71</v>
       </c>
       <c r="R18" t="n">
+        <v>74</v>
+      </c>
+      <c r="S18" t="n">
         <v>32</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>37.6</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>31.8</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>51.2</v>
       </c>
-      <c r="V18" t="n">
-        <v>11</v>
-      </c>
       <c r="W18" t="n">
-        <v>0.968642927159866</v>
-      </c>
-      <c r="X18" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.6949002939959208</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1917,30 +1973,33 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>95.4192</v>
+        <v>76</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.34</v>
+        <v>71</v>
       </c>
       <c r="R19" t="n">
+        <v>74</v>
+      </c>
+      <c r="S19" t="n">
         <v>32</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>37.6</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>32.2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>51.6</v>
       </c>
-      <c r="V19" t="n">
-        <v>11</v>
-      </c>
       <c r="W19" t="n">
-        <v>0.7529984581000377</v>
-      </c>
-      <c r="X19" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.6724670417245586</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -1995,30 +2054,33 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>94.2192</v>
+        <v>76</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.1</v>
+        <v>71</v>
       </c>
       <c r="R20" t="n">
+        <v>74</v>
+      </c>
+      <c r="S20" t="n">
         <v>32.4</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>37.8</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>32.4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>52</v>
       </c>
-      <c r="V20" t="n">
-        <v>11</v>
-      </c>
       <c r="W20" t="n">
-        <v>0.5876256685443731</v>
-      </c>
-      <c r="X20" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6647440140666306</v>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2073,30 +2135,33 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>93.0192</v>
+        <v>76</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.74</v>
+        <v>71</v>
       </c>
       <c r="R21" t="n">
+        <v>74</v>
+      </c>
+      <c r="S21" t="n">
         <v>32.8</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>38</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>31.8</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>51.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>11</v>
-      </c>
       <c r="W21" t="n">
-        <v>0.8352354186823991</v>
-      </c>
-      <c r="X21" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.704309857352493</v>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2151,30 +2216,33 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.74</v>
+        <v>71</v>
       </c>
       <c r="R22" t="n">
+        <v>74</v>
+      </c>
+      <c r="S22" t="n">
         <v>33.2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>38.6</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>31</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>50.6</v>
       </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.202290167929526</v>
-      </c>
-      <c r="X22" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.7833797547088727</v>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2229,30 +2297,33 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>94.2</v>
+        <v>76</v>
       </c>
       <c r="Q23" t="n">
-        <v>19.1</v>
+        <v>71</v>
       </c>
       <c r="R23" t="n">
+        <v>74</v>
+      </c>
+      <c r="S23" t="n">
         <v>32.6</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>38.2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>30.6</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>50.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>11</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.439690704771102</v>
-      </c>
-      <c r="X23" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.7897654838421074</v>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2307,30 +2378,33 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q24" t="n">
-        <v>19.5</v>
+        <v>71</v>
       </c>
       <c r="R24" t="n">
+        <v>74</v>
+      </c>
+      <c r="S24" t="n">
         <v>32.2</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>37.8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>31</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>51</v>
       </c>
-      <c r="V24" t="n">
-        <v>11</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.396653177878337</v>
-      </c>
-      <c r="X24" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.736411287063924</v>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2385,30 +2459,33 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q25" t="n">
-        <v>20.26</v>
+        <v>71</v>
       </c>
       <c r="R25" t="n">
+        <v>74</v>
+      </c>
+      <c r="S25" t="n">
         <v>32</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>37.6</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>31</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>51.4</v>
       </c>
-      <c r="V25" t="n">
-        <v>11</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.396536525171807</v>
-      </c>
-      <c r="X25" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.7172724612356758</v>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2463,30 +2540,33 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>97.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.36</v>
+        <v>71</v>
       </c>
       <c r="R26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S26" t="n">
         <v>32.2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>37.2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>31</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>51.6</v>
       </c>
-      <c r="V26" t="n">
-        <v>11</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.202186322423641</v>
-      </c>
-      <c r="X26" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.7016094425817545</v>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2541,30 +2621,33 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.56</v>
+        <v>71</v>
       </c>
       <c r="R27" t="n">
+        <v>74</v>
+      </c>
+      <c r="S27" t="n">
         <v>32.4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>37.2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>31.4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>51.8</v>
       </c>
-      <c r="V27" t="n">
-        <v>11</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.100662321690227</v>
-      </c>
-      <c r="X27" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.6798901284948231</v>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2619,30 +2702,33 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q28" t="n">
-        <v>23.2</v>
+        <v>71</v>
       </c>
       <c r="R28" t="n">
+        <v>74</v>
+      </c>
+      <c r="S28" t="n">
         <v>33.2</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>38.2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>31.2</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>51.4</v>
       </c>
-      <c r="V28" t="n">
-        <v>11</v>
-      </c>
       <c r="W28" t="n">
-        <v>0.9755063212816936</v>
-      </c>
-      <c r="X28" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.7343075357206406</v>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2697,30 +2783,33 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>98.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.6</v>
+        <v>71</v>
       </c>
       <c r="R29" t="n">
+        <v>74</v>
+      </c>
+      <c r="S29" t="n">
         <v>33.6</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>38.8</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>30.4</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>50.8</v>
       </c>
-      <c r="V29" t="n">
-        <v>11</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.338126081559071</v>
-      </c>
-      <c r="X29" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.8155236206807137</v>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -2775,30 +2864,33 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q30" t="n">
-        <v>19.46</v>
+        <v>71</v>
       </c>
       <c r="R30" t="n">
+        <v>74</v>
+      </c>
+      <c r="S30" t="n">
         <v>33.8</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>39.2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>30</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>50.4</v>
       </c>
-      <c r="V30" t="n">
-        <v>11</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.747983376571871</v>
-      </c>
-      <c r="X30" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.8680825589701621</v>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -2853,30 +2945,33 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="Q31" t="n">
-        <v>18.66</v>
+        <v>71</v>
       </c>
       <c r="R31" t="n">
+        <v>74</v>
+      </c>
+      <c r="S31" t="n">
         <v>33.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>39.4</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>29.8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>50.6</v>
       </c>
-      <c r="V31" t="n">
-        <v>11</v>
-      </c>
       <c r="W31" t="n">
-        <v>2.115499696559791</v>
-      </c>
-      <c r="X31" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.879759551269695</v>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -2931,30 +3026,33 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>101.8</v>
+        <v>76</v>
       </c>
       <c r="Q32" t="n">
-        <v>19.06</v>
+        <v>71</v>
       </c>
       <c r="R32" t="n">
+        <v>74</v>
+      </c>
+      <c r="S32" t="n">
         <v>33.4</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>39.2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>29.6</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>50.8</v>
       </c>
-      <c r="V32" t="n">
-        <v>11</v>
-      </c>
       <c r="W32" t="n">
-        <v>2.044584152434128</v>
-      </c>
-      <c r="X32" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.875055516418532</v>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -3009,32 +3107,35 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>98.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q33" t="n">
-        <v>20.26</v>
+        <v>71</v>
       </c>
       <c r="R33" t="n">
+        <v>74</v>
+      </c>
+      <c r="S33" t="n">
         <v>32.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>37.6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>29.8</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>51.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.500505867683878</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.7750205709531822</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -3087,30 +3188,33 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q34" t="n">
-        <v>21.86</v>
+        <v>71</v>
       </c>
       <c r="R34" t="n">
+        <v>74</v>
+      </c>
+      <c r="S34" t="n">
         <v>32.6</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>37</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>30.2</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>52.8</v>
       </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
       <c r="W34" t="n">
-        <v>0.9743511567322202</v>
-      </c>
-      <c r="X34" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.712726414666253</v>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3165,30 +3269,33 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>92.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>23.32</v>
+        <v>71</v>
       </c>
       <c r="R35" t="n">
+        <v>74</v>
+      </c>
+      <c r="S35" t="n">
         <v>32.6</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>36.6</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>30.6</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>53.2</v>
       </c>
-      <c r="V35" t="n">
-        <v>11</v>
-      </c>
       <c r="W35" t="n">
-        <v>0.7575259953029985</v>
-      </c>
-      <c r="X35" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.6830800038643214</v>
+      </c>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3243,30 +3350,33 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>91</v>
+        <v>76.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.12</v>
+        <v>70.8</v>
       </c>
       <c r="R36" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S36" t="n">
         <v>32.6</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>36.6</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>30.4</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>53.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>11</v>
-      </c>
       <c r="W36" t="n">
-        <v>0.908068696843122</v>
-      </c>
-      <c r="X36" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.826478422789262</v>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3321,30 +3431,33 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>89.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.62</v>
+        <v>70.8</v>
       </c>
       <c r="R37" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S37" t="n">
         <v>32.6</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>36.8</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>30.4</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>52.8</v>
       </c>
-      <c r="V37" t="n">
-        <v>11</v>
-      </c>
       <c r="W37" t="n">
-        <v>1.223751356713466</v>
-      </c>
-      <c r="X37" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.8348352916095348</v>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3399,32 +3512,35 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>91.2</v>
+        <v>76.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>19.62</v>
+        <v>70.8</v>
       </c>
       <c r="R38" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S38" t="n">
         <v>32.8</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>37.2</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>30.2</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>51.8</v>
       </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
       <c r="W38" t="n">
-        <v>1.412327334290264</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.871549538229629</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3477,30 +3593,33 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>92.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>17.88</v>
+        <v>70.8</v>
       </c>
       <c r="R39" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S39" t="n">
         <v>32.2</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>36.4</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>30.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>51.6</v>
       </c>
-      <c r="V39" t="n">
-        <v>11</v>
-      </c>
       <c r="W39" t="n">
-        <v>1.627508791747056</v>
-      </c>
-      <c r="X39" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.8635688308331333</v>
+      </c>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -3555,32 +3674,35 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q40" t="n">
-        <v>18.3</v>
+        <v>70.8</v>
       </c>
       <c r="R40" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S40" t="n">
         <v>31.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>36.2</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>30.4</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>52</v>
       </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
       <c r="W40" t="n">
-        <v>1.555384767149065</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.8369903036432276</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -3633,30 +3755,33 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>91.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q41" t="n">
-        <v>19.88</v>
+        <v>71</v>
       </c>
       <c r="R41" t="n">
+        <v>74</v>
+      </c>
+      <c r="S41" t="n">
         <v>30.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>36</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>31</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>52.4</v>
       </c>
-      <c r="V41" t="n">
-        <v>11</v>
-      </c>
       <c r="W41" t="n">
-        <v>1.325279502329801</v>
-      </c>
-      <c r="X41" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.670523719633403</v>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3711,30 +3836,33 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>91.2</v>
+        <v>76</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.38</v>
+        <v>71</v>
       </c>
       <c r="R42" t="n">
+        <v>74</v>
+      </c>
+      <c r="S42" t="n">
         <v>29.2</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>35.6</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>31.4</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>53.2</v>
       </c>
-      <c r="V42" t="n">
-        <v>11</v>
-      </c>
       <c r="W42" t="n">
-        <v>1.101691121913319</v>
-      </c>
-      <c r="X42" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.649489354871001</v>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3789,30 +3917,33 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q43" t="n">
-        <v>22.5</v>
+        <v>71</v>
       </c>
       <c r="R43" t="n">
+        <v>74</v>
+      </c>
+      <c r="S43" t="n">
         <v>29.2</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>37</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>31.6</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>54</v>
       </c>
-      <c r="V43" t="n">
-        <v>11</v>
-      </c>
       <c r="W43" t="n">
-        <v>0.9769675351613281</v>
-      </c>
-      <c r="X43" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.6441921145534092</v>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3867,30 +3998,33 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>90.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q44" t="n">
-        <v>22.98</v>
+        <v>71</v>
       </c>
       <c r="R44" t="n">
+        <v>74</v>
+      </c>
+      <c r="S44" t="n">
         <v>30</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>38.6</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>31.6</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>53.4</v>
       </c>
-      <c r="V44" t="n">
-        <v>11</v>
-      </c>
       <c r="W44" t="n">
-        <v>0.9706163953336694</v>
-      </c>
-      <c r="X44" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.6935528576194641</v>
+      </c>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -3945,30 +4079,33 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>89.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q45" t="n">
-        <v>21.78</v>
+        <v>71</v>
       </c>
       <c r="R45" t="n">
+        <v>74</v>
+      </c>
+      <c r="S45" t="n">
         <v>31</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>39.4</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>31.4</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>52.8</v>
       </c>
-      <c r="V45" t="n">
-        <v>11</v>
-      </c>
       <c r="W45" t="n">
-        <v>1.272750149269682</v>
-      </c>
-      <c r="X45" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.7419814386346163</v>
+      </c>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4023,32 +4160,35 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>88.2</v>
+        <v>76</v>
       </c>
       <c r="Q46" t="n">
-        <v>19.5</v>
+        <v>71</v>
       </c>
       <c r="R46" t="n">
+        <v>74</v>
+      </c>
+      <c r="S46" t="n">
         <v>31.2</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>38.4</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>30.8</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>52.2</v>
       </c>
-      <c r="V46" t="n">
-        <v>11</v>
-      </c>
       <c r="W46" t="n">
-        <v>1.678909918886715</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.732056679612874</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -4101,32 +4241,35 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>90.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q47" t="n">
-        <v>18.1</v>
+        <v>71</v>
       </c>
       <c r="R47" t="n">
+        <v>74</v>
+      </c>
+      <c r="S47" t="n">
         <v>31.6</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>37.6</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>31</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>52</v>
       </c>
-      <c r="V47" t="n">
-        <v>11</v>
-      </c>
       <c r="W47" t="n">
-        <v>1.673707932012941</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.6998543740398395</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -4179,32 +4322,35 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q48" t="n">
-        <v>18.5</v>
+        <v>71</v>
       </c>
       <c r="R48" t="n">
+        <v>74</v>
+      </c>
+      <c r="S48" t="n">
         <v>31</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>36</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>31.4</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>51.8</v>
       </c>
-      <c r="V48" t="n">
-        <v>11</v>
-      </c>
       <c r="W48" t="n">
-        <v>1.511205410684532</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.6638043450859197</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -4257,30 +4403,33 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q49" t="n">
-        <v>20.16</v>
+        <v>71</v>
       </c>
       <c r="R49" t="n">
+        <v>74</v>
+      </c>
+      <c r="S49" t="n">
         <v>30.4</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>35.2</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>31.8</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>52.2</v>
       </c>
-      <c r="V49" t="n">
-        <v>11</v>
-      </c>
       <c r="W49" t="n">
-        <v>1.196539917505262</v>
-      </c>
-      <c r="X49" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.6449403350362493</v>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4335,30 +4484,33 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.76</v>
+        <v>71</v>
       </c>
       <c r="R50" t="n">
+        <v>74</v>
+      </c>
+      <c r="S50" t="n">
         <v>30.2</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>34.4</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>32</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>52.6</v>
       </c>
-      <c r="V50" t="n">
-        <v>11</v>
-      </c>
       <c r="W50" t="n">
-        <v>0.92874132525353</v>
-      </c>
-      <c r="X50" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.6443545689518031</v>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4413,30 +4565,33 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q51" t="n">
-        <v>22.98</v>
+        <v>71</v>
       </c>
       <c r="R51" t="n">
+        <v>74</v>
+      </c>
+      <c r="S51" t="n">
         <v>30.8</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>35.8</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>32.2</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>52.8</v>
       </c>
-      <c r="V51" t="n">
-        <v>11</v>
-      </c>
       <c r="W51" t="n">
-        <v>0.7558402647500382</v>
-      </c>
-      <c r="X51" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.6143342318798544</v>
+      </c>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4491,30 +4646,33 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.46</v>
+        <v>71</v>
       </c>
       <c r="R52" t="n">
+        <v>74</v>
+      </c>
+      <c r="S52" t="n">
         <v>31.2</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>37</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>31.6</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>52.6</v>
       </c>
-      <c r="V52" t="n">
-        <v>11</v>
-      </c>
       <c r="W52" t="n">
-        <v>0.6631242116026222</v>
-      </c>
-      <c r="X52" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.6469046853576438</v>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4569,30 +4727,33 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q53" t="n">
-        <v>22.34</v>
+        <v>71</v>
       </c>
       <c r="R53" t="n">
+        <v>74</v>
+      </c>
+      <c r="S53" t="n">
         <v>31.6</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>38.2</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>31</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>52.4</v>
       </c>
-      <c r="V53" t="n">
-        <v>11</v>
-      </c>
       <c r="W53" t="n">
-        <v>0.8940674924279982</v>
-      </c>
-      <c r="X53" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.7098400590788566</v>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4647,30 +4808,33 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.2</v>
+        <v>71</v>
       </c>
       <c r="R54" t="n">
+        <v>74</v>
+      </c>
+      <c r="S54" t="n">
         <v>32</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>38.6</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>30.4</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>51.6</v>
       </c>
-      <c r="V54" t="n">
-        <v>11</v>
-      </c>
       <c r="W54" t="n">
-        <v>1.259191373143324</v>
-      </c>
-      <c r="X54" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.7747379226963952</v>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4725,32 +4889,35 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q55" t="n">
-        <v>18.68</v>
+        <v>71</v>
       </c>
       <c r="R55" t="n">
+        <v>74</v>
+      </c>
+      <c r="S55" t="n">
         <v>32</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>38.8</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>30.2</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>51.4</v>
       </c>
-      <c r="V55" t="n">
-        <v>11</v>
-      </c>
       <c r="W55" t="n">
-        <v>1.540015325733564</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.7991440195704616</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -4803,30 +4970,33 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.64</v>
+        <v>71</v>
       </c>
       <c r="R56" t="n">
+        <v>74</v>
+      </c>
+      <c r="S56" t="n">
         <v>31.8</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>38</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>30.6</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>51.6</v>
       </c>
-      <c r="V56" t="n">
-        <v>11</v>
-      </c>
       <c r="W56" t="n">
-        <v>1.341561021368795</v>
-      </c>
-      <c r="X56" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.7423371546210885</v>
+      </c>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4881,30 +5051,33 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q57" t="n">
-        <v>21.56</v>
+        <v>71</v>
       </c>
       <c r="R57" t="n">
+        <v>74</v>
+      </c>
+      <c r="S57" t="n">
         <v>31.8</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>37.6</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>31</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>51.8</v>
       </c>
-      <c r="V57" t="n">
-        <v>11</v>
-      </c>
       <c r="W57" t="n">
-        <v>1.027869800998514</v>
-      </c>
-      <c r="X57" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.7052684296767091</v>
+      </c>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -4959,30 +5132,33 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.16</v>
+        <v>71</v>
       </c>
       <c r="R58" t="n">
+        <v>74</v>
+      </c>
+      <c r="S58" t="n">
         <v>31.8</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>37.2</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>31.4</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>52</v>
       </c>
-      <c r="V58" t="n">
-        <v>11</v>
-      </c>
       <c r="W58" t="n">
-        <v>0.7661925919692026</v>
-      </c>
-      <c r="X58" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.6728187541890239</v>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5037,30 +5213,33 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q59" t="n">
-        <v>24.7</v>
+        <v>71</v>
       </c>
       <c r="R59" t="n">
+        <v>74</v>
+      </c>
+      <c r="S59" t="n">
         <v>31.8</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>37.2</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>31.4</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>52.8</v>
       </c>
-      <c r="V59" t="n">
-        <v>11</v>
-      </c>
       <c r="W59" t="n">
-        <v>0.5566566467991361</v>
-      </c>
-      <c r="X59" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.6535284850729371</v>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5115,30 +5294,33 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>95.8</v>
+        <v>76</v>
       </c>
       <c r="Q60" t="n">
-        <v>25.22</v>
+        <v>71</v>
       </c>
       <c r="R60" t="n">
+        <v>74</v>
+      </c>
+      <c r="S60" t="n">
         <v>32.2</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>37.8</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>31.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>52.8</v>
       </c>
-      <c r="V60" t="n">
-        <v>11</v>
-      </c>
       <c r="W60" t="n">
-        <v>0.5712313794104241</v>
-      </c>
-      <c r="X60" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.6793374377188223</v>
+      </c>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5193,30 +5375,33 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q61" t="n">
-        <v>23.8</v>
+        <v>71</v>
       </c>
       <c r="R61" t="n">
+        <v>74</v>
+      </c>
+      <c r="S61" t="n">
         <v>32.6</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>38.6</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>30.8</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>52.4</v>
       </c>
-      <c r="V61" t="n">
-        <v>11</v>
-      </c>
       <c r="W61" t="n">
-        <v>1.036269918287342</v>
-      </c>
-      <c r="X61" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.7370823961201343</v>
+      </c>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5271,30 +5456,33 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q62" t="n">
-        <v>21.4</v>
+        <v>71</v>
       </c>
       <c r="R62" t="n">
+        <v>74</v>
+      </c>
+      <c r="S62" t="n">
         <v>32.8</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>39</v>
       </c>
-      <c r="T62" t="n">
+      <c r="U62" t="n">
         <v>30.4</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>52</v>
       </c>
-      <c r="V62" t="n">
-        <v>11</v>
-      </c>
       <c r="W62" t="n">
-        <v>1.229783388160766</v>
-      </c>
-      <c r="X62" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.7844928027238821</v>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5349,30 +5537,33 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q63" t="n">
-        <v>21.4</v>
+        <v>71</v>
       </c>
       <c r="R63" t="n">
+        <v>74</v>
+      </c>
+      <c r="S63" t="n">
         <v>32.2</v>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="n">
         <v>38.6</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>29.8</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>51.6</v>
       </c>
-      <c r="V63" t="n">
-        <v>11</v>
-      </c>
       <c r="W63" t="n">
-        <v>1.229763393239584</v>
-      </c>
-      <c r="X63" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.8097100690642924</v>
+      </c>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5427,30 +5618,33 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q64" t="n">
-        <v>22.28</v>
+        <v>71</v>
       </c>
       <c r="R64" t="n">
+        <v>74</v>
+      </c>
+      <c r="S64" t="n">
         <v>32</v>
       </c>
-      <c r="S64" t="n">
+      <c r="T64" t="n">
         <v>38.2</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>30.2</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>51.8</v>
       </c>
-      <c r="V64" t="n">
-        <v>11</v>
-      </c>
       <c r="W64" t="n">
-        <v>1.070300626573916</v>
-      </c>
-      <c r="X64" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.7656208229401038</v>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5505,30 +5699,33 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q65" t="n">
-        <v>23.44</v>
+        <v>71</v>
       </c>
       <c r="R65" t="n">
+        <v>74</v>
+      </c>
+      <c r="S65" t="n">
         <v>31.4</v>
       </c>
-      <c r="S65" t="n">
+      <c r="T65" t="n">
         <v>37.4</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>30.6</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>52.2</v>
       </c>
-      <c r="V65" t="n">
-        <v>11</v>
-      </c>
       <c r="W65" t="n">
-        <v>0.8491801084694517</v>
-      </c>
-      <c r="X65" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.7094290488534267</v>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5583,30 +5780,33 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q66" t="n">
-        <v>24.44</v>
+        <v>71</v>
       </c>
       <c r="R66" t="n">
+        <v>74</v>
+      </c>
+      <c r="S66" t="n">
         <v>31.4</v>
       </c>
-      <c r="S66" t="n">
+      <c r="T66" t="n">
         <v>37.4</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>30.8</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>52.4</v>
       </c>
-      <c r="V66" t="n">
-        <v>11</v>
-      </c>
       <c r="W66" t="n">
-        <v>0.5809934400407808</v>
-      </c>
-      <c r="X66" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.6943450323756959</v>
+      </c>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5661,30 +5861,33 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q67" t="n">
-        <v>25.34</v>
+        <v>71</v>
       </c>
       <c r="R67" t="n">
+        <v>74</v>
+      </c>
+      <c r="S67" t="n">
         <v>31.4</v>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="n">
         <v>37.4</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>31</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>52.6</v>
       </c>
-      <c r="V67" t="n">
-        <v>11</v>
-      </c>
       <c r="W67" t="n">
-        <v>0.5415687080225249</v>
-      </c>
-      <c r="X67" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.6802059607473228</v>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5739,30 +5942,33 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q68" t="n">
-        <v>23.72</v>
+        <v>71</v>
       </c>
       <c r="R68" t="n">
+        <v>74</v>
+      </c>
+      <c r="S68" t="n">
         <v>32.2</v>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="n">
         <v>38.6</v>
       </c>
-      <c r="T68" t="n">
+      <c r="U68" t="n">
         <v>31.4</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>52.6</v>
       </c>
-      <c r="V68" t="n">
-        <v>11</v>
-      </c>
       <c r="W68" t="n">
-        <v>0.7460398337512737</v>
-      </c>
-      <c r="X68" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.7061962468080312</v>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5817,30 +6023,33 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q69" t="n">
-        <v>21.36</v>
+        <v>71</v>
       </c>
       <c r="R69" t="n">
+        <v>74</v>
+      </c>
+      <c r="S69" t="n">
         <v>32.6</v>
       </c>
-      <c r="S69" t="n">
+      <c r="T69" t="n">
         <v>39</v>
       </c>
-      <c r="T69" t="n">
+      <c r="U69" t="n">
         <v>30.8</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>51.8</v>
       </c>
-      <c r="V69" t="n">
-        <v>11</v>
-      </c>
       <c r="W69" t="n">
-        <v>1.101376616224521</v>
-      </c>
-      <c r="X69" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.7688394251672708</v>
+      </c>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5895,30 +6104,33 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>95.2</v>
+        <v>76</v>
       </c>
       <c r="Q70" t="n">
-        <v>19.2</v>
+        <v>71</v>
       </c>
       <c r="R70" t="n">
+        <v>74</v>
+      </c>
+      <c r="S70" t="n">
         <v>33</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>39.4</v>
       </c>
-      <c r="T70" t="n">
+      <c r="U70" t="n">
         <v>30.4</v>
       </c>
-      <c r="U70" t="n">
+      <c r="V70" t="n">
         <v>51</v>
       </c>
-      <c r="V70" t="n">
-        <v>11</v>
-      </c>
       <c r="W70" t="n">
-        <v>1.464419179617352</v>
-      </c>
-      <c r="X70" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.8309412280749596</v>
+      </c>
+      <c r="Y70" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -5973,32 +6185,35 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q71" t="n">
-        <v>19.4</v>
+        <v>71</v>
       </c>
       <c r="R71" t="n">
+        <v>74</v>
+      </c>
+      <c r="S71" t="n">
         <v>33</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>39.4</v>
       </c>
-      <c r="T71" t="n">
+      <c r="U71" t="n">
         <v>30.2</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>50.6</v>
       </c>
-      <c r="V71" t="n">
-        <v>11</v>
-      </c>
       <c r="W71" t="n">
-        <v>1.495402425763014</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Healthy (Optimal Performance)</t>
+        <v>16</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.8533624891154367</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -6051,30 +6266,33 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>96.2</v>
+        <v>76</v>
       </c>
       <c r="Q72" t="n">
-        <v>20.7</v>
+        <v>71</v>
       </c>
       <c r="R72" t="n">
+        <v>74</v>
+      </c>
+      <c r="S72" t="n">
         <v>33</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>38.8</v>
       </c>
-      <c r="T72" t="n">
+      <c r="U72" t="n">
         <v>30.6</v>
       </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
         <v>50.8</v>
       </c>
-      <c r="V72" t="n">
-        <v>11</v>
-      </c>
       <c r="W72" t="n">
-        <v>1.265368697505385</v>
-      </c>
-      <c r="X72" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.8008202253363524</v>
+      </c>
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6129,30 +6347,33 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q73" t="n">
-        <v>22.32</v>
+        <v>71</v>
       </c>
       <c r="R73" t="n">
+        <v>74</v>
+      </c>
+      <c r="S73" t="n">
         <v>33</v>
       </c>
-      <c r="S73" t="n">
+      <c r="T73" t="n">
         <v>38.2</v>
       </c>
-      <c r="T73" t="n">
+      <c r="U73" t="n">
         <v>30.6</v>
       </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
         <v>51.2</v>
       </c>
-      <c r="V73" t="n">
-        <v>11</v>
-      </c>
       <c r="W73" t="n">
-        <v>1.032686933417325</v>
-      </c>
-      <c r="X73" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.7654235126251563</v>
+      </c>
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6207,30 +6428,33 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="Q74" t="n">
-        <v>23.64</v>
+        <v>71</v>
       </c>
       <c r="R74" t="n">
+        <v>74</v>
+      </c>
+      <c r="S74" t="n">
         <v>33.6</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>38.2</v>
       </c>
-      <c r="T74" t="n">
+      <c r="U74" t="n">
         <v>31.2</v>
       </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
         <v>52</v>
       </c>
-      <c r="V74" t="n">
-        <v>11</v>
-      </c>
       <c r="W74" t="n">
-        <v>0.9183118126408456</v>
-      </c>
-      <c r="X74" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.7214310892925622</v>
+      </c>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6285,30 +6509,33 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>97.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q75" t="n">
-        <v>24.54</v>
+        <v>71</v>
       </c>
       <c r="R75" t="n">
+        <v>74</v>
+      </c>
+      <c r="S75" t="n">
         <v>33.8</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>38.6</v>
       </c>
-      <c r="T75" t="n">
+      <c r="U75" t="n">
         <v>31.4</v>
       </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
         <v>52.4</v>
       </c>
-      <c r="V75" t="n">
-        <v>11</v>
-      </c>
       <c r="W75" t="n">
-        <v>0.8850468523551512</v>
-      </c>
-      <c r="X75" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7225873962586025</v>
+      </c>
+      <c r="Y75" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6363,30 +6590,33 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q76" t="n">
-        <v>23.14</v>
+        <v>71</v>
       </c>
       <c r="R76" t="n">
+        <v>74</v>
+      </c>
+      <c r="S76" t="n">
         <v>34</v>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>39</v>
       </c>
-      <c r="T76" t="n">
+      <c r="U76" t="n">
         <v>31.6</v>
       </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
         <v>52.8</v>
       </c>
-      <c r="V76" t="n">
-        <v>11</v>
-      </c>
       <c r="W76" t="n">
-        <v>0.8088814981365265</v>
-      </c>
-      <c r="X76" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.7285922955789707</v>
+      </c>
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6441,30 +6671,33 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q77" t="n">
-        <v>20.86</v>
+        <v>71</v>
       </c>
       <c r="R77" t="n">
+        <v>74</v>
+      </c>
+      <c r="S77" t="n">
         <v>32.6</v>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="n">
         <v>38.4</v>
       </c>
-      <c r="T77" t="n">
+      <c r="U77" t="n">
         <v>31</v>
       </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
         <v>52.4</v>
       </c>
-      <c r="V77" t="n">
-        <v>11</v>
-      </c>
       <c r="W77" t="n">
-        <v>1.127643132058594</v>
-      </c>
-      <c r="X77" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0.7197975292004871</v>
+      </c>
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6519,30 +6752,33 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="Q78" t="n">
-        <v>20.66</v>
+        <v>71</v>
       </c>
       <c r="R78" t="n">
+        <v>74</v>
+      </c>
+      <c r="S78" t="n">
         <v>31.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>37.4</v>
       </c>
-      <c r="T78" t="n">
+      <c r="U78" t="n">
         <v>30.8</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
         <v>52.2</v>
       </c>
-      <c r="V78" t="n">
-        <v>11</v>
-      </c>
       <c r="W78" t="n">
-        <v>1.249242059455916</v>
-      </c>
-      <c r="X78" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.6991137862507599</v>
+      </c>
+      <c r="Y78" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6597,30 +6833,33 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="Q79" t="n">
-        <v>21.7</v>
+        <v>71</v>
       </c>
       <c r="R79" t="n">
+        <v>74</v>
+      </c>
+      <c r="S79" t="n">
         <v>29.6</v>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>36.2</v>
       </c>
-      <c r="T79" t="n">
+      <c r="U79" t="n">
         <v>30.4</v>
       </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
         <v>51.8</v>
       </c>
-      <c r="V79" t="n">
-        <v>11</v>
-      </c>
       <c r="W79" t="n">
-        <v>1.209196809384445</v>
-      </c>
-      <c r="X79" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.7247651631504363</v>
+      </c>
+      <c r="Y79" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6675,30 +6914,33 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="Q80" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="R80" t="n">
+        <v>74</v>
+      </c>
+      <c r="S80" t="n">
         <v>28.2</v>
       </c>
-      <c r="S80" t="n">
+      <c r="T80" t="n">
         <v>34.6</v>
       </c>
-      <c r="T80" t="n">
+      <c r="U80" t="n">
         <v>30.2</v>
       </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
         <v>51.8</v>
       </c>
-      <c r="V80" t="n">
-        <v>11</v>
-      </c>
       <c r="W80" t="n">
-        <v>1.205786134539605</v>
-      </c>
-      <c r="X80" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.7669093126055212</v>
+      </c>
+      <c r="Y80" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6753,30 +6995,33 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>89.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q81" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="R81" t="n">
+        <v>74</v>
+      </c>
+      <c r="S81" t="n">
         <v>28</v>
       </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
         <v>34.2</v>
       </c>
-      <c r="T81" t="n">
+      <c r="U81" t="n">
         <v>30.2</v>
       </c>
-      <c r="U81" t="n">
+      <c r="V81" t="n">
         <v>51.8</v>
       </c>
-      <c r="V81" t="n">
-        <v>11</v>
-      </c>
       <c r="W81" t="n">
-        <v>1.048796146858556</v>
-      </c>
-      <c r="X81" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0.7785155172763627</v>
+      </c>
+      <c r="Y81" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6831,30 +7076,33 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>90.2</v>
+        <v>76</v>
       </c>
       <c r="Q82" t="n">
-        <v>25.02</v>
+        <v>71</v>
       </c>
       <c r="R82" t="n">
+        <v>74</v>
+      </c>
+      <c r="S82" t="n">
         <v>29.4</v>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
         <v>35.4</v>
       </c>
-      <c r="T82" t="n">
+      <c r="U82" t="n">
         <v>30.4</v>
       </c>
-      <c r="U82" t="n">
+      <c r="V82" t="n">
         <v>52</v>
       </c>
-      <c r="V82" t="n">
-        <v>11</v>
-      </c>
       <c r="W82" t="n">
-        <v>0.8485232367993599</v>
-      </c>
-      <c r="X82" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0.7216147375345103</v>
+      </c>
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6909,30 +7157,33 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q83" t="n">
-        <v>23.74</v>
+        <v>71</v>
       </c>
       <c r="R83" t="n">
+        <v>74</v>
+      </c>
+      <c r="S83" t="n">
         <v>30.6</v>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="n">
         <v>36.6</v>
       </c>
-      <c r="T83" t="n">
+      <c r="U83" t="n">
         <v>30.6</v>
       </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
         <v>52</v>
       </c>
-      <c r="V83" t="n">
-        <v>11</v>
-      </c>
       <c r="W83" t="n">
-        <v>0.7396425372065808</v>
-      </c>
-      <c r="X83" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.7026870655448694</v>
+      </c>
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -6987,30 +7238,33 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="Q84" t="n">
-        <v>21.26</v>
+        <v>71</v>
       </c>
       <c r="R84" t="n">
+        <v>74</v>
+      </c>
+      <c r="S84" t="n">
         <v>31.8</v>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="n">
         <v>37.8</v>
       </c>
-      <c r="T84" t="n">
+      <c r="U84" t="n">
         <v>30.8</v>
       </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
         <v>52</v>
       </c>
-      <c r="V84" t="n">
-        <v>11</v>
-      </c>
       <c r="W84" t="n">
-        <v>1.055421671177767</v>
-      </c>
-      <c r="X84" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0.7151714006539636</v>
+      </c>
+      <c r="Y84" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7065,30 +7319,33 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q85" t="n">
-        <v>20.64</v>
+        <v>71</v>
       </c>
       <c r="R85" t="n">
+        <v>74</v>
+      </c>
+      <c r="S85" t="n">
         <v>32.6</v>
       </c>
-      <c r="S85" t="n">
+      <c r="T85" t="n">
         <v>38.6</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>31.2</v>
       </c>
-      <c r="U85" t="n">
+      <c r="V85" t="n">
         <v>52.2</v>
       </c>
-      <c r="V85" t="n">
-        <v>11</v>
-      </c>
       <c r="W85" t="n">
-        <v>1.158438876880804</v>
-      </c>
-      <c r="X85" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.7242952378371186</v>
+      </c>
+      <c r="Y85" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7143,30 +7400,33 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>93.8</v>
+        <v>76</v>
       </c>
       <c r="Q86" t="n">
-        <v>21.68</v>
+        <v>71</v>
       </c>
       <c r="R86" t="n">
+        <v>74</v>
+      </c>
+      <c r="S86" t="n">
         <v>32.2</v>
       </c>
-      <c r="S86" t="n">
+      <c r="T86" t="n">
         <v>38.2</v>
       </c>
-      <c r="T86" t="n">
+      <c r="U86" t="n">
         <v>31.4</v>
       </c>
-      <c r="U86" t="n">
+      <c r="V86" t="n">
         <v>52.4</v>
       </c>
-      <c r="V86" t="n">
-        <v>11</v>
-      </c>
       <c r="W86" t="n">
-        <v>0.9753947838207709</v>
-      </c>
-      <c r="X86" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.6942190746586999</v>
+      </c>
+      <c r="Y86" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7221,30 +7481,33 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q87" t="n">
-        <v>22.54</v>
+        <v>71</v>
       </c>
       <c r="R87" t="n">
+        <v>74</v>
+      </c>
+      <c r="S87" t="n">
         <v>32.4</v>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="n">
         <v>37.6</v>
       </c>
-      <c r="T87" t="n">
+      <c r="U87" t="n">
         <v>31.8</v>
       </c>
-      <c r="U87" t="n">
+      <c r="V87" t="n">
         <v>53</v>
       </c>
-      <c r="V87" t="n">
-        <v>11</v>
-      </c>
       <c r="W87" t="n">
-        <v>0.8602841590645481</v>
-      </c>
-      <c r="X87" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.6482483318912819</v>
+      </c>
+      <c r="Y87" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7299,30 +7562,33 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q88" t="n">
-        <v>23.68</v>
+        <v>71</v>
       </c>
       <c r="R88" t="n">
+        <v>74</v>
+      </c>
+      <c r="S88" t="n">
         <v>32.6</v>
       </c>
-      <c r="S88" t="n">
+      <c r="T88" t="n">
         <v>37.4</v>
       </c>
-      <c r="T88" t="n">
+      <c r="U88" t="n">
         <v>32</v>
       </c>
-      <c r="U88" t="n">
+      <c r="V88" t="n">
         <v>53</v>
       </c>
-      <c r="V88" t="n">
-        <v>11</v>
-      </c>
       <c r="W88" t="n">
-        <v>0.7217005850543328</v>
-      </c>
-      <c r="X88" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0.6379000282114469</v>
+      </c>
+      <c r="Y88" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7377,30 +7643,33 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q89" t="n">
-        <v>24.68</v>
+        <v>71</v>
       </c>
       <c r="R89" t="n">
+        <v>74</v>
+      </c>
+      <c r="S89" t="n">
         <v>32.6</v>
       </c>
-      <c r="S89" t="n">
+      <c r="T89" t="n">
         <v>37.2</v>
       </c>
-      <c r="T89" t="n">
+      <c r="U89" t="n">
         <v>32</v>
       </c>
-      <c r="U89" t="n">
+      <c r="V89" t="n">
         <v>53</v>
       </c>
-      <c r="V89" t="n">
-        <v>11</v>
-      </c>
       <c r="W89" t="n">
-        <v>0.5346580786656381</v>
-      </c>
-      <c r="X89" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0.6326413979515344</v>
+      </c>
+      <c r="Y89" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7455,30 +7724,33 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q90" t="n">
-        <v>23.36</v>
+        <v>71</v>
       </c>
       <c r="R90" t="n">
+        <v>74</v>
+      </c>
+      <c r="S90" t="n">
         <v>33</v>
       </c>
-      <c r="S90" t="n">
+      <c r="T90" t="n">
         <v>37.4</v>
       </c>
-      <c r="T90" t="n">
+      <c r="U90" t="n">
         <v>31.8</v>
       </c>
-      <c r="U90" t="n">
+      <c r="V90" t="n">
         <v>52.8</v>
       </c>
-      <c r="V90" t="n">
-        <v>11</v>
-      </c>
       <c r="W90" t="n">
-        <v>0.8733671820544582</v>
-      </c>
-      <c r="X90" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0.6502219638916007</v>
+      </c>
+      <c r="Y90" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7533,30 +7805,33 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q91" t="n">
-        <v>21.32</v>
+        <v>71</v>
       </c>
       <c r="R91" t="n">
+        <v>74</v>
+      </c>
+      <c r="S91" t="n">
         <v>33.4</v>
       </c>
-      <c r="S91" t="n">
+      <c r="T91" t="n">
         <v>37.4</v>
       </c>
-      <c r="T91" t="n">
+      <c r="U91" t="n">
         <v>32</v>
       </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
         <v>53</v>
       </c>
-      <c r="V91" t="n">
-        <v>11</v>
-      </c>
       <c r="W91" t="n">
-        <v>1.419579667684974</v>
-      </c>
-      <c r="X91" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0.6446334473008913</v>
+      </c>
+      <c r="Y91" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7611,30 +7886,33 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>99.8</v>
+        <v>76</v>
       </c>
       <c r="Q92" t="n">
-        <v>21.56</v>
+        <v>71</v>
       </c>
       <c r="R92" t="n">
+        <v>74</v>
+      </c>
+      <c r="S92" t="n">
         <v>33</v>
       </c>
-      <c r="S92" t="n">
+      <c r="T92" t="n">
         <v>37.6</v>
       </c>
-      <c r="T92" t="n">
+      <c r="U92" t="n">
         <v>31.8</v>
       </c>
-      <c r="U92" t="n">
+      <c r="V92" t="n">
         <v>52.8</v>
       </c>
-      <c r="V92" t="n">
-        <v>11</v>
-      </c>
       <c r="W92" t="n">
-        <v>1.423272439861389</v>
-      </c>
-      <c r="X92" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0.6560021580304347</v>
+      </c>
+      <c r="Y92" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7689,30 +7967,33 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="Q93" t="n">
-        <v>22.14</v>
+        <v>71</v>
       </c>
       <c r="R93" t="n">
+        <v>74</v>
+      </c>
+      <c r="S93" t="n">
         <v>32.6</v>
       </c>
-      <c r="S93" t="n">
+      <c r="T93" t="n">
         <v>37.4</v>
       </c>
-      <c r="T93" t="n">
+      <c r="U93" t="n">
         <v>31.8</v>
       </c>
-      <c r="U93" t="n">
+      <c r="V93" t="n">
         <v>53.2</v>
       </c>
-      <c r="V93" t="n">
-        <v>11</v>
-      </c>
       <c r="W93" t="n">
-        <v>1.381643846748345</v>
-      </c>
-      <c r="X93" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0.6397937803917858</v>
+      </c>
+      <c r="Y93" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7767,30 +8048,33 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q94" t="n">
-        <v>22.34</v>
+        <v>71</v>
       </c>
       <c r="R94" t="n">
+        <v>74</v>
+      </c>
+      <c r="S94" t="n">
         <v>32.8</v>
       </c>
-      <c r="S94" t="n">
+      <c r="T94" t="n">
         <v>37.8</v>
       </c>
-      <c r="T94" t="n">
+      <c r="U94" t="n">
         <v>31.8</v>
       </c>
-      <c r="U94" t="n">
+      <c r="V94" t="n">
         <v>53</v>
       </c>
-      <c r="V94" t="n">
-        <v>11</v>
-      </c>
       <c r="W94" t="n">
-        <v>1.314865247078792</v>
-      </c>
-      <c r="X94" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0.6569737433260721</v>
+      </c>
+      <c r="Y94" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7845,30 +8129,33 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q95" t="n">
-        <v>22.7</v>
+        <v>71</v>
       </c>
       <c r="R95" t="n">
+        <v>74</v>
+      </c>
+      <c r="S95" t="n">
         <v>33</v>
       </c>
-      <c r="S95" t="n">
+      <c r="T95" t="n">
         <v>37.8</v>
       </c>
-      <c r="T95" t="n">
+      <c r="U95" t="n">
         <v>31.8</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>52.8</v>
       </c>
-      <c r="V95" t="n">
-        <v>11</v>
-      </c>
       <c r="W95" t="n">
-        <v>1.281989157802651</v>
-      </c>
-      <c r="X95" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0.6623880900028085</v>
+      </c>
+      <c r="Y95" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -7923,30 +8210,33 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>98.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q96" t="n">
-        <v>22.1</v>
+        <v>71</v>
       </c>
       <c r="R96" t="n">
+        <v>74</v>
+      </c>
+      <c r="S96" t="n">
         <v>33.2</v>
       </c>
-      <c r="S96" t="n">
+      <c r="T96" t="n">
         <v>38</v>
       </c>
-      <c r="T96" t="n">
+      <c r="U96" t="n">
         <v>31.4</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>52.2</v>
       </c>
-      <c r="V96" t="n">
-        <v>11</v>
-      </c>
       <c r="W96" t="n">
-        <v>1.210930558027211</v>
-      </c>
-      <c r="X96" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0.6976350107712581</v>
+      </c>
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8001,32 +8291,35 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="Q97" t="n">
-        <v>19.94</v>
+        <v>71</v>
       </c>
       <c r="R97" t="n">
+        <v>74</v>
+      </c>
+      <c r="S97" t="n">
         <v>33.4</v>
       </c>
-      <c r="S97" t="n">
+      <c r="T97" t="n">
         <v>37.6</v>
       </c>
-      <c r="T97" t="n">
+      <c r="U97" t="n">
         <v>31</v>
       </c>
-      <c r="U97" t="n">
+      <c r="V97" t="n">
         <v>51.4</v>
       </c>
-      <c r="V97" t="n">
-        <v>11</v>
-      </c>
       <c r="W97" t="n">
-        <v>1.557574557602033</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0.7252949508540458</v>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8079,30 +8372,33 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>97.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q98" t="n">
-        <v>19.72</v>
+        <v>71</v>
       </c>
       <c r="R98" t="n">
+        <v>74</v>
+      </c>
+      <c r="S98" t="n">
         <v>33.2</v>
       </c>
-      <c r="S98" t="n">
+      <c r="T98" t="n">
         <v>37.8</v>
       </c>
-      <c r="T98" t="n">
+      <c r="U98" t="n">
         <v>31</v>
       </c>
-      <c r="U98" t="n">
+      <c r="V98" t="n">
         <v>51.2</v>
       </c>
-      <c r="V98" t="n">
-        <v>11</v>
-      </c>
       <c r="W98" t="n">
-        <v>1.464998973366844</v>
-      </c>
-      <c r="X98" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0.7354855384153599</v>
+      </c>
+      <c r="Y98" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8157,30 +8453,33 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q99" t="n">
-        <v>20.12</v>
+        <v>71</v>
       </c>
       <c r="R99" t="n">
+        <v>74</v>
+      </c>
+      <c r="S99" t="n">
         <v>32.6</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
         <v>37.4</v>
       </c>
-      <c r="T99" t="n">
+      <c r="U99" t="n">
         <v>31.2</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>51.6</v>
       </c>
-      <c r="V99" t="n">
-        <v>11</v>
-      </c>
       <c r="W99" t="n">
-        <v>1.303778929320417</v>
-      </c>
-      <c r="X99" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0.6994194325842142</v>
+      </c>
+      <c r="Y99" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8235,30 +8534,33 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="Q100" t="n">
-        <v>20.3</v>
+        <v>71</v>
       </c>
       <c r="R100" t="n">
+        <v>74</v>
+      </c>
+      <c r="S100" t="n">
         <v>32.4</v>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
         <v>37.8</v>
       </c>
-      <c r="T100" t="n">
+      <c r="U100" t="n">
         <v>31.6</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>52</v>
       </c>
-      <c r="V100" t="n">
-        <v>11</v>
-      </c>
       <c r="W100" t="n">
-        <v>1.188633534988764</v>
-      </c>
-      <c r="X100" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0.6838870287226405</v>
+      </c>
+      <c r="Y100" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8313,30 +8615,33 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q101" t="n">
-        <v>20.76</v>
+        <v>71</v>
       </c>
       <c r="R101" t="n">
+        <v>74</v>
+      </c>
+      <c r="S101" t="n">
         <v>32.2</v>
       </c>
-      <c r="S101" t="n">
+      <c r="T101" t="n">
         <v>38.2</v>
       </c>
-      <c r="T101" t="n">
+      <c r="U101" t="n">
         <v>31.4</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>51.8</v>
       </c>
-      <c r="V101" t="n">
-        <v>11</v>
-      </c>
       <c r="W101" t="n">
-        <v>1.141047739382975</v>
-      </c>
-      <c r="X101" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0.7094838194839073</v>
+      </c>
+      <c r="Y101" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8391,30 +8696,33 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>92.8</v>
+        <v>76</v>
       </c>
       <c r="Q102" t="n">
-        <v>20.68</v>
+        <v>71</v>
       </c>
       <c r="R102" t="n">
+        <v>74</v>
+      </c>
+      <c r="S102" t="n">
         <v>32.2</v>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="n">
         <v>39</v>
       </c>
-      <c r="T102" t="n">
+      <c r="U102" t="n">
         <v>31.6</v>
       </c>
-      <c r="U102" t="n">
+      <c r="V102" t="n">
         <v>51.6</v>
       </c>
-      <c r="V102" t="n">
-        <v>11</v>
-      </c>
       <c r="W102" t="n">
-        <v>1.179259210578447</v>
-      </c>
-      <c r="X102" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0.7424698171610137</v>
+      </c>
+      <c r="Y102" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8469,30 +8777,33 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q103" t="n">
-        <v>19.06</v>
+        <v>71</v>
       </c>
       <c r="R103" t="n">
+        <v>74</v>
+      </c>
+      <c r="S103" t="n">
         <v>32.6</v>
       </c>
-      <c r="S103" t="n">
+      <c r="T103" t="n">
         <v>39.2</v>
       </c>
-      <c r="T103" t="n">
+      <c r="U103" t="n">
         <v>31.4</v>
       </c>
-      <c r="U103" t="n">
+      <c r="V103" t="n">
         <v>50.8</v>
       </c>
-      <c r="V103" t="n">
-        <v>11</v>
-      </c>
       <c r="W103" t="n">
-        <v>1.450878128345426</v>
-      </c>
-      <c r="X103" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0.7843084665696156</v>
+      </c>
+      <c r="Y103" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -8547,32 +8858,35 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q104" t="n">
-        <v>18.06</v>
+        <v>71</v>
       </c>
       <c r="R104" t="n">
+        <v>74</v>
+      </c>
+      <c r="S104" t="n">
         <v>33</v>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="n">
         <v>39</v>
       </c>
-      <c r="T104" t="n">
+      <c r="U104" t="n">
         <v>31.4</v>
       </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>50.4</v>
       </c>
-      <c r="V104" t="n">
-        <v>11</v>
-      </c>
       <c r="W104" t="n">
-        <v>1.67434528311299</v>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0.7912183843674583</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8625,32 +8939,35 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>99.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q105" t="n">
-        <v>17.26</v>
+        <v>71</v>
       </c>
       <c r="R105" t="n">
+        <v>74</v>
+      </c>
+      <c r="S105" t="n">
         <v>33</v>
       </c>
-      <c r="S105" t="n">
+      <c r="T105" t="n">
         <v>38.8</v>
       </c>
-      <c r="T105" t="n">
+      <c r="U105" t="n">
         <v>31</v>
       </c>
-      <c r="U105" t="n">
+      <c r="V105" t="n">
         <v>50</v>
       </c>
-      <c r="V105" t="n">
-        <v>11</v>
-      </c>
       <c r="W105" t="n">
-        <v>1.995771884714499</v>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0.8117727929153128</v>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8703,32 +9020,35 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>100.4</v>
+        <v>76</v>
       </c>
       <c r="Q106" t="n">
-        <v>16.88</v>
+        <v>71</v>
       </c>
       <c r="R106" t="n">
+        <v>74</v>
+      </c>
+      <c r="S106" t="n">
         <v>33</v>
       </c>
-      <c r="S106" t="n">
+      <c r="T106" t="n">
         <v>38.6</v>
       </c>
-      <c r="T106" t="n">
+      <c r="U106" t="n">
         <v>31.2</v>
       </c>
-      <c r="U106" t="n">
+      <c r="V106" t="n">
         <v>50.2</v>
       </c>
-      <c r="V106" t="n">
-        <v>11</v>
-      </c>
       <c r="W106" t="n">
-        <v>2.130324483473926</v>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0.7887020123496812</v>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8781,32 +9101,35 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>99.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q107" t="n">
-        <v>16.38</v>
+        <v>71</v>
       </c>
       <c r="R107" t="n">
+        <v>74</v>
+      </c>
+      <c r="S107" t="n">
         <v>32.6</v>
       </c>
-      <c r="S107" t="n">
+      <c r="T107" t="n">
         <v>38.6</v>
       </c>
-      <c r="T107" t="n">
+      <c r="U107" t="n">
         <v>31</v>
       </c>
-      <c r="U107" t="n">
+      <c r="V107" t="n">
         <v>50.6</v>
       </c>
-      <c r="V107" t="n">
-        <v>11</v>
-      </c>
       <c r="W107" t="n">
-        <v>2.108896199872318</v>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0.7795592596069739</v>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8859,32 +9182,35 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q108" t="n">
-        <v>16.58</v>
+        <v>71</v>
       </c>
       <c r="R108" t="n">
+        <v>74</v>
+      </c>
+      <c r="S108" t="n">
         <v>32</v>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="n">
         <v>38.6</v>
       </c>
-      <c r="T108" t="n">
+      <c r="U108" t="n">
         <v>31</v>
       </c>
-      <c r="U108" t="n">
+      <c r="V108" t="n">
         <v>51.2</v>
       </c>
-      <c r="V108" t="n">
-        <v>11</v>
-      </c>
       <c r="W108" t="n">
-        <v>1.981466452866876</v>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0.757889467964371</v>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -8937,32 +9263,35 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q109" t="n">
-        <v>16.78</v>
+        <v>71.2</v>
       </c>
       <c r="R109" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S109" t="n">
         <v>32</v>
       </c>
-      <c r="S109" t="n">
+      <c r="T109" t="n">
         <v>39.2</v>
       </c>
-      <c r="T109" t="n">
+      <c r="U109" t="n">
         <v>31</v>
       </c>
-      <c r="U109" t="n">
+      <c r="V109" t="n">
         <v>51.8</v>
       </c>
-      <c r="V109" t="n">
-        <v>11</v>
-      </c>
       <c r="W109" t="n">
-        <v>1.872872366683723</v>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0.6601423227860383</v>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9015,32 +9344,35 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q110" t="n">
-        <v>17.18</v>
+        <v>71.2</v>
       </c>
       <c r="R110" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S110" t="n">
         <v>32</v>
       </c>
-      <c r="S110" t="n">
+      <c r="T110" t="n">
         <v>39.4</v>
       </c>
-      <c r="T110" t="n">
+      <c r="U110" t="n">
         <v>31.2</v>
       </c>
-      <c r="U110" t="n">
+      <c r="V110" t="n">
         <v>52</v>
       </c>
-      <c r="V110" t="n">
-        <v>11</v>
-      </c>
       <c r="W110" t="n">
-        <v>1.74216603374881</v>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0.6568667314439534</v>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9093,32 +9425,35 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q111" t="n">
-        <v>17.3</v>
+        <v>71.2</v>
       </c>
       <c r="R111" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S111" t="n">
         <v>32.6</v>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="n">
         <v>39.6</v>
       </c>
-      <c r="T111" t="n">
+      <c r="U111" t="n">
         <v>31.4</v>
       </c>
-      <c r="U111" t="n">
+      <c r="V111" t="n">
         <v>51.8</v>
       </c>
-      <c r="V111" t="n">
-        <v>11</v>
-      </c>
       <c r="W111" t="n">
-        <v>1.740327070655982</v>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0.6689452655623817</v>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9171,32 +9506,35 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q112" t="n">
-        <v>17.24</v>
+        <v>71.2</v>
       </c>
       <c r="R112" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S112" t="n">
         <v>33.6</v>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="n">
         <v>39.8</v>
       </c>
-      <c r="T112" t="n">
+      <c r="U112" t="n">
         <v>31.8</v>
       </c>
-      <c r="U112" t="n">
+      <c r="V112" t="n">
         <v>51.6</v>
       </c>
-      <c r="V112" t="n">
-        <v>11</v>
-      </c>
       <c r="W112" t="n">
-        <v>1.735804592551996</v>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0.6830028780329384</v>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9249,32 +9587,35 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>93.2</v>
+        <v>76</v>
       </c>
       <c r="Q113" t="n">
-        <v>16.28</v>
+        <v>71.2</v>
       </c>
       <c r="R113" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="S113" t="n">
         <v>33</v>
       </c>
-      <c r="S113" t="n">
+      <c r="T113" t="n">
         <v>38.6</v>
       </c>
-      <c r="T113" t="n">
+      <c r="U113" t="n">
         <v>32</v>
       </c>
-      <c r="U113" t="n">
+      <c r="V113" t="n">
         <v>52</v>
       </c>
-      <c r="V113" t="n">
-        <v>11</v>
-      </c>
       <c r="W113" t="n">
-        <v>1.863057090201996</v>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0.5882435826783569</v>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9327,32 +9668,35 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>92.8</v>
+        <v>76</v>
       </c>
       <c r="Q114" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R114" t="n">
+        <v>74</v>
+      </c>
+      <c r="S114" t="n">
         <v>32.2</v>
       </c>
-      <c r="S114" t="n">
+      <c r="T114" t="n">
         <v>37.6</v>
       </c>
-      <c r="T114" t="n">
+      <c r="U114" t="n">
         <v>31.8</v>
       </c>
-      <c r="U114" t="n">
+      <c r="V114" t="n">
         <v>52.2</v>
       </c>
-      <c r="V114" t="n">
-        <v>11</v>
-      </c>
       <c r="W114" t="n">
-        <v>1.820721614708353</v>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0.6654646041160845</v>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9405,32 +9749,35 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q115" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R115" t="n">
+        <v>74</v>
+      </c>
+      <c r="S115" t="n">
         <v>31.4</v>
       </c>
-      <c r="S115" t="n">
+      <c r="T115" t="n">
         <v>36.8</v>
       </c>
-      <c r="T115" t="n">
+      <c r="U115" t="n">
         <v>31.6</v>
       </c>
-      <c r="U115" t="n">
+      <c r="V115" t="n">
         <v>52.8</v>
       </c>
-      <c r="V115" t="n">
-        <v>11</v>
-      </c>
       <c r="W115" t="n">
-        <v>1.715406197645129</v>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0.6381106970527153</v>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9483,32 +9830,35 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q116" t="n">
-        <v>17.28</v>
+        <v>71</v>
       </c>
       <c r="R116" t="n">
+        <v>74</v>
+      </c>
+      <c r="S116" t="n">
         <v>30.6</v>
       </c>
-      <c r="S116" t="n">
+      <c r="T116" t="n">
         <v>36.4</v>
       </c>
-      <c r="T116" t="n">
+      <c r="U116" t="n">
         <v>31.8</v>
       </c>
-      <c r="U116" t="n">
+      <c r="V116" t="n">
         <v>53.6</v>
       </c>
-      <c r="V116" t="n">
-        <v>11</v>
-      </c>
       <c r="W116" t="n">
-        <v>1.665816432579006</v>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0.6154736691935769</v>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9561,32 +9911,35 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>94.8</v>
+        <v>76</v>
       </c>
       <c r="Q117" t="n">
-        <v>17.58</v>
+        <v>71</v>
       </c>
       <c r="R117" t="n">
+        <v>74</v>
+      </c>
+      <c r="S117" t="n">
         <v>29.8</v>
       </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>36</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>31.8</v>
       </c>
-      <c r="U117" t="n">
+      <c r="V117" t="n">
         <v>54.4</v>
       </c>
-      <c r="V117" t="n">
-        <v>11</v>
-      </c>
       <c r="W117" t="n">
-        <v>1.614993157332795</v>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.6128416929031025</v>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9639,32 +9992,35 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q118" t="n">
-        <v>17.62</v>
+        <v>71</v>
       </c>
       <c r="R118" t="n">
+        <v>74</v>
+      </c>
+      <c r="S118" t="n">
         <v>30.8</v>
       </c>
-      <c r="S118" t="n">
+      <c r="T118" t="n">
         <v>37</v>
       </c>
-      <c r="T118" t="n">
+      <c r="U118" t="n">
         <v>31.8</v>
       </c>
-      <c r="U118" t="n">
+      <c r="V118" t="n">
         <v>54.4</v>
       </c>
-      <c r="V118" t="n">
-        <v>11</v>
-      </c>
       <c r="W118" t="n">
-        <v>1.629522108820776</v>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.6161513110940933</v>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9717,32 +10073,35 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q119" t="n">
-        <v>16.22</v>
+        <v>71</v>
       </c>
       <c r="R119" t="n">
+        <v>74</v>
+      </c>
+      <c r="S119" t="n">
         <v>30.4</v>
       </c>
-      <c r="S119" t="n">
+      <c r="T119" t="n">
         <v>36.4</v>
       </c>
-      <c r="T119" t="n">
+      <c r="U119" t="n">
         <v>31.6</v>
       </c>
-      <c r="U119" t="n">
+      <c r="V119" t="n">
         <v>53.4</v>
       </c>
-      <c r="V119" t="n">
-        <v>11</v>
-      </c>
       <c r="W119" t="n">
-        <v>1.842935755349468</v>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.6267708395291222</v>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9795,32 +10154,35 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q120" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R120" t="n">
+        <v>74</v>
+      </c>
+      <c r="S120" t="n">
         <v>30</v>
       </c>
-      <c r="S120" t="n">
+      <c r="T120" t="n">
         <v>36.6</v>
       </c>
-      <c r="T120" t="n">
+      <c r="U120" t="n">
         <v>31.8</v>
       </c>
-      <c r="U120" t="n">
+      <c r="V120" t="n">
         <v>53.4</v>
       </c>
-      <c r="V120" t="n">
-        <v>11</v>
-      </c>
       <c r="W120" t="n">
-        <v>1.822091584629359</v>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.6267782131685651</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9873,32 +10235,35 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q121" t="n">
-        <v>17.58</v>
+        <v>71</v>
       </c>
       <c r="R121" t="n">
+        <v>74</v>
+      </c>
+      <c r="S121" t="n">
         <v>29</v>
       </c>
-      <c r="S121" t="n">
+      <c r="T121" t="n">
         <v>36.4</v>
       </c>
-      <c r="T121" t="n">
+      <c r="U121" t="n">
         <v>31.6</v>
       </c>
-      <c r="U121" t="n">
+      <c r="V121" t="n">
         <v>53.6</v>
       </c>
-      <c r="V121" t="n">
-        <v>11</v>
-      </c>
       <c r="W121" t="n">
-        <v>1.640116656989666</v>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.6426545725236403</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -9951,30 +10316,33 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>94.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q122" t="n">
-        <v>18.78</v>
+        <v>71</v>
       </c>
       <c r="R122" t="n">
+        <v>74</v>
+      </c>
+      <c r="S122" t="n">
         <v>29</v>
       </c>
-      <c r="S122" t="n">
+      <c r="T122" t="n">
         <v>36.4</v>
       </c>
-      <c r="T122" t="n">
+      <c r="U122" t="n">
         <v>31.8</v>
       </c>
-      <c r="U122" t="n">
+      <c r="V122" t="n">
         <v>53.6</v>
       </c>
-      <c r="V122" t="n">
-        <v>11</v>
-      </c>
       <c r="W122" t="n">
-        <v>1.418021016037323</v>
-      </c>
-      <c r="X122" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.6361502645042215</v>
+      </c>
+      <c r="Y122" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10029,30 +10397,33 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q123" t="n">
-        <v>19.42</v>
+        <v>71</v>
       </c>
       <c r="R123" t="n">
+        <v>74</v>
+      </c>
+      <c r="S123" t="n">
         <v>28.2</v>
       </c>
-      <c r="S123" t="n">
+      <c r="T123" t="n">
         <v>35.6</v>
       </c>
-      <c r="T123" t="n">
+      <c r="U123" t="n">
         <v>31.6</v>
       </c>
-      <c r="U123" t="n">
+      <c r="V123" t="n">
         <v>53.6</v>
       </c>
-      <c r="V123" t="n">
-        <v>11</v>
-      </c>
       <c r="W123" t="n">
-        <v>1.32777002573984</v>
-      </c>
-      <c r="X123" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.6556691986635085</v>
+      </c>
+      <c r="Y123" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10107,30 +10478,33 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>96.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q124" t="n">
-        <v>20.38</v>
+        <v>71</v>
       </c>
       <c r="R124" t="n">
+        <v>74</v>
+      </c>
+      <c r="S124" t="n">
         <v>29</v>
       </c>
-      <c r="S124" t="n">
+      <c r="T124" t="n">
         <v>36.8</v>
       </c>
-      <c r="T124" t="n">
+      <c r="U124" t="n">
         <v>32</v>
       </c>
-      <c r="U124" t="n">
+      <c r="V124" t="n">
         <v>54.6</v>
       </c>
-      <c r="V124" t="n">
-        <v>11</v>
-      </c>
       <c r="W124" t="n">
-        <v>1.227638480421958</v>
-      </c>
-      <c r="X124" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.6277310918793374</v>
+      </c>
+      <c r="Y124" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10185,30 +10559,33 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>94.2</v>
+        <v>76</v>
       </c>
       <c r="Q125" t="n">
-        <v>19.72</v>
+        <v>71</v>
       </c>
       <c r="R125" t="n">
+        <v>74</v>
+      </c>
+      <c r="S125" t="n">
         <v>29.8</v>
       </c>
-      <c r="S125" t="n">
+      <c r="T125" t="n">
         <v>37</v>
       </c>
-      <c r="T125" t="n">
+      <c r="U125" t="n">
         <v>31.6</v>
       </c>
-      <c r="U125" t="n">
+      <c r="V125" t="n">
         <v>53.8</v>
       </c>
-      <c r="V125" t="n">
-        <v>11</v>
-      </c>
       <c r="W125" t="n">
-        <v>1.260504791517507</v>
-      </c>
-      <c r="X125" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.637517181278484</v>
+      </c>
+      <c r="Y125" t="inlineStr">
         <is>
           <t>Healthy (Optimal Performance)</t>
         </is>
@@ -10263,32 +10640,35 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q126" t="n">
-        <v>18.22</v>
+        <v>71</v>
       </c>
       <c r="R126" t="n">
+        <v>74</v>
+      </c>
+      <c r="S126" t="n">
         <v>30.6</v>
       </c>
-      <c r="S126" t="n">
+      <c r="T126" t="n">
         <v>37.2</v>
       </c>
-      <c r="T126" t="n">
+      <c r="U126" t="n">
         <v>31.2</v>
       </c>
-      <c r="U126" t="n">
+      <c r="V126" t="n">
         <v>53</v>
       </c>
-      <c r="V126" t="n">
-        <v>11</v>
-      </c>
       <c r="W126" t="n">
-        <v>1.527570963556832</v>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.6618152389928876</v>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -10341,32 +10721,35 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q127" t="n">
-        <v>16.92</v>
+        <v>71</v>
       </c>
       <c r="R127" t="n">
+        <v>74</v>
+      </c>
+      <c r="S127" t="n">
         <v>30.2</v>
       </c>
-      <c r="S127" t="n">
+      <c r="T127" t="n">
         <v>36.8</v>
       </c>
-      <c r="T127" t="n">
+      <c r="U127" t="n">
         <v>30.4</v>
       </c>
-      <c r="U127" t="n">
+      <c r="V127" t="n">
         <v>52.4</v>
       </c>
-      <c r="V127" t="n">
-        <v>11</v>
-      </c>
       <c r="W127" t="n">
-        <v>1.786313218554695</v>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.7101233491605563</v>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -10419,32 +10802,35 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q128" t="n">
-        <v>17.2</v>
+        <v>71</v>
       </c>
       <c r="R128" t="n">
+        <v>74</v>
+      </c>
+      <c r="S128" t="n">
         <v>30</v>
       </c>
-      <c r="S128" t="n">
+      <c r="T128" t="n">
         <v>36.4</v>
       </c>
-      <c r="T128" t="n">
+      <c r="U128" t="n">
         <v>30</v>
       </c>
-      <c r="U128" t="n">
+      <c r="V128" t="n">
         <v>52.4</v>
       </c>
-      <c r="V128" t="n">
-        <v>11</v>
-      </c>
       <c r="W128" t="n">
-        <v>1.749786709647528</v>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.731433505143956</v>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -10497,32 +10883,35 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>89.2</v>
+        <v>76</v>
       </c>
       <c r="Q129" t="n">
-        <v>17.92</v>
+        <v>71</v>
       </c>
       <c r="R129" t="n">
+        <v>74</v>
+      </c>
+      <c r="S129" t="n">
         <v>29.8</v>
       </c>
-      <c r="S129" t="n">
+      <c r="T129" t="n">
         <v>36.6</v>
       </c>
-      <c r="T129" t="n">
+      <c r="U129" t="n">
         <v>29.6</v>
       </c>
-      <c r="U129" t="n">
+      <c r="V129" t="n">
         <v>52.2</v>
       </c>
-      <c r="V129" t="n">
-        <v>11</v>
-      </c>
       <c r="W129" t="n">
-        <v>1.816535406930937</v>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.7669107765522384</v>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -10575,32 +10964,35 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q130" t="n">
-        <v>17.74</v>
+        <v>70.8</v>
       </c>
       <c r="R130" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S130" t="n">
         <v>30.2</v>
       </c>
-      <c r="S130" t="n">
+      <c r="T130" t="n">
         <v>36.6</v>
       </c>
-      <c r="T130" t="n">
+      <c r="U130" t="n">
         <v>29.6</v>
       </c>
-      <c r="U130" t="n">
+      <c r="V130" t="n">
         <v>52.6</v>
       </c>
-      <c r="V130" t="n">
-        <v>11</v>
-      </c>
       <c r="W130" t="n">
-        <v>1.717553687026597</v>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.9559311342447585</v>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10653,32 +11045,35 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>90.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q131" t="n">
-        <v>17.44</v>
+        <v>70.8</v>
       </c>
       <c r="R131" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S131" t="n">
         <v>29</v>
       </c>
-      <c r="S131" t="n">
+      <c r="T131" t="n">
         <v>35.6</v>
       </c>
-      <c r="T131" t="n">
+      <c r="U131" t="n">
         <v>29.2</v>
       </c>
-      <c r="U131" t="n">
+      <c r="V131" t="n">
         <v>52.4</v>
       </c>
-      <c r="V131" t="n">
-        <v>11</v>
-      </c>
       <c r="W131" t="n">
-        <v>1.79314235522775</v>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.989573086019329</v>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10731,32 +11126,35 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>92.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q132" t="n">
-        <v>17.46</v>
+        <v>70.8</v>
       </c>
       <c r="R132" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S132" t="n">
         <v>28.8</v>
       </c>
-      <c r="S132" t="n">
+      <c r="T132" t="n">
         <v>35.8</v>
       </c>
-      <c r="T132" t="n">
+      <c r="U132" t="n">
         <v>29.2</v>
       </c>
-      <c r="U132" t="n">
+      <c r="V132" t="n">
         <v>52.6</v>
       </c>
-      <c r="V132" t="n">
-        <v>11</v>
-      </c>
       <c r="W132" t="n">
-        <v>1.730184101592871</v>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.9887310228737625</v>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10809,32 +11207,35 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>92.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q133" t="n">
-        <v>17.74</v>
+        <v>70.8</v>
       </c>
       <c r="R133" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S133" t="n">
         <v>29.2</v>
       </c>
-      <c r="S133" t="n">
+      <c r="T133" t="n">
         <v>36.8</v>
       </c>
-      <c r="T133" t="n">
+      <c r="U133" t="n">
         <v>29.2</v>
       </c>
-      <c r="U133" t="n">
+      <c r="V133" t="n">
         <v>52</v>
       </c>
-      <c r="V133" t="n">
-        <v>11</v>
-      </c>
       <c r="W133" t="n">
-        <v>1.692266086197723</v>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1.000020478275454</v>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10887,32 +11288,35 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>92.2</v>
+        <v>75.8</v>
       </c>
       <c r="Q134" t="n">
-        <v>17.5</v>
+        <v>70.8</v>
       </c>
       <c r="R134" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="S134" t="n">
         <v>29</v>
       </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
         <v>36.4</v>
       </c>
-      <c r="T134" t="n">
+      <c r="U134" t="n">
         <v>29</v>
       </c>
-      <c r="U134" t="n">
+      <c r="V134" t="n">
         <v>51.4</v>
       </c>
-      <c r="V134" t="n">
-        <v>11</v>
-      </c>
       <c r="W134" t="n">
-        <v>1.743222793649444</v>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X134" t="n">
+        <v>1.013759537224972</v>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -10965,32 +11369,35 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="Q135" t="n">
-        <v>16.88</v>
+        <v>71</v>
       </c>
       <c r="R135" t="n">
+        <v>74</v>
+      </c>
+      <c r="S135" t="n">
         <v>28.6</v>
       </c>
-      <c r="S135" t="n">
+      <c r="T135" t="n">
         <v>36.2</v>
       </c>
-      <c r="T135" t="n">
+      <c r="U135" t="n">
         <v>29.2</v>
       </c>
-      <c r="U135" t="n">
+      <c r="V135" t="n">
         <v>51</v>
       </c>
-      <c r="V135" t="n">
-        <v>11</v>
-      </c>
       <c r="W135" t="n">
-        <v>1.820853319350763</v>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.8448925359604099</v>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11043,32 +11450,35 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>93.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q136" t="n">
-        <v>16.98</v>
+        <v>71</v>
       </c>
       <c r="R136" t="n">
+        <v>74</v>
+      </c>
+      <c r="S136" t="n">
         <v>30.2</v>
       </c>
-      <c r="S136" t="n">
+      <c r="T136" t="n">
         <v>36.4</v>
       </c>
-      <c r="T136" t="n">
+      <c r="U136" t="n">
         <v>23.84</v>
       </c>
-      <c r="U136" t="n">
+      <c r="V136" t="n">
         <v>51.2</v>
       </c>
-      <c r="V136" t="n">
-        <v>-1</v>
-      </c>
       <c r="W136" t="n">
-        <v>3</v>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>21</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.134017693081558</v>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11121,32 +11531,35 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>94.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Q137" t="n">
-        <v>16.48</v>
+        <v>71</v>
       </c>
       <c r="R137" t="n">
+        <v>74</v>
+      </c>
+      <c r="S137" t="n">
         <v>30</v>
       </c>
-      <c r="S137" t="n">
+      <c r="T137" t="n">
         <v>35.8</v>
       </c>
-      <c r="T137" t="n">
+      <c r="U137" t="n">
         <v>23.64</v>
       </c>
-      <c r="U137" t="n">
+      <c r="V137" t="n">
         <v>51</v>
       </c>
-      <c r="V137" t="n">
-        <v>-1</v>
-      </c>
       <c r="W137" t="n">
-        <v>3</v>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>21</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.07464763933678618</v>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11199,32 +11612,35 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>95.8</v>
+        <v>76.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>14.58</v>
+        <v>71</v>
       </c>
       <c r="R138" t="n">
+        <v>74</v>
+      </c>
+      <c r="S138" t="n">
         <v>30</v>
       </c>
-      <c r="S138" t="n">
+      <c r="T138" t="n">
         <v>34.8</v>
       </c>
-      <c r="T138" t="n">
+      <c r="U138" t="n">
         <v>23.64</v>
       </c>
-      <c r="U138" t="n">
+      <c r="V138" t="n">
         <v>51.2</v>
       </c>
-      <c r="V138" t="n">
-        <v>-1</v>
-      </c>
       <c r="W138" t="n">
-        <v>3</v>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>21</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.05433573851580063</v>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11277,32 +11693,35 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q139" t="n">
-        <v>14.32</v>
+        <v>71</v>
       </c>
       <c r="R139" t="n">
+        <v>74</v>
+      </c>
+      <c r="S139" t="n">
         <v>30</v>
       </c>
-      <c r="S139" t="n">
+      <c r="T139" t="n">
         <v>34.6</v>
       </c>
-      <c r="T139" t="n">
+      <c r="U139" t="n">
         <v>23.64</v>
       </c>
-      <c r="U139" t="n">
+      <c r="V139" t="n">
         <v>51.4</v>
       </c>
-      <c r="V139" t="n">
-        <v>-1</v>
-      </c>
       <c r="W139" t="n">
-        <v>3</v>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>21</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.08126100792241692</v>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11355,32 +11774,35 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>95.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q140" t="n">
-        <v>15.7</v>
+        <v>71</v>
       </c>
       <c r="R140" t="n">
+        <v>74</v>
+      </c>
+      <c r="S140" t="n">
         <v>29.6</v>
       </c>
-      <c r="S140" t="n">
+      <c r="T140" t="n">
         <v>34.4</v>
       </c>
-      <c r="T140" t="n">
+      <c r="U140" t="n">
         <v>23.24</v>
       </c>
-      <c r="U140" t="n">
+      <c r="V140" t="n">
         <v>51.6</v>
       </c>
-      <c r="V140" t="n">
-        <v>-1</v>
-      </c>
       <c r="W140" t="n">
-        <v>3</v>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>21</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.1127775807872971</v>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11433,32 +11855,35 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="Q141" t="n">
-        <v>16.22</v>
+        <v>71</v>
       </c>
       <c r="R141" t="n">
+        <v>74</v>
+      </c>
+      <c r="S141" t="n">
         <v>29.4</v>
       </c>
-      <c r="S141" t="n">
+      <c r="T141" t="n">
         <v>35.2</v>
       </c>
-      <c r="T141" t="n">
+      <c r="U141" t="n">
         <v>29</v>
       </c>
-      <c r="U141" t="n">
+      <c r="V141" t="n">
         <v>51.8</v>
       </c>
-      <c r="V141" t="n">
-        <v>11</v>
-      </c>
       <c r="W141" t="n">
-        <v>1.992723574870719</v>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.8219270751894857</v>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11511,32 +11936,35 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="Q142" t="n">
-        <v>17.12</v>
+        <v>71</v>
       </c>
       <c r="R142" t="n">
+        <v>74</v>
+      </c>
+      <c r="S142" t="n">
         <v>29.8</v>
       </c>
-      <c r="S142" t="n">
+      <c r="T142" t="n">
         <v>34.8</v>
       </c>
-      <c r="T142" t="n">
+      <c r="U142" t="n">
         <v>29.2</v>
       </c>
-      <c r="U142" t="n">
+      <c r="V142" t="n">
         <v>52</v>
       </c>
-      <c r="V142" t="n">
-        <v>11</v>
-      </c>
       <c r="W142" t="n">
-        <v>1.800424238433738</v>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.8018320442679482</v>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11589,32 +12017,35 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>94.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q143" t="n">
-        <v>18.06</v>
+        <v>71</v>
       </c>
       <c r="R143" t="n">
+        <v>74</v>
+      </c>
+      <c r="S143" t="n">
         <v>29.4</v>
       </c>
-      <c r="S143" t="n">
+      <c r="T143" t="n">
         <v>34.8</v>
       </c>
-      <c r="T143" t="n">
+      <c r="U143" t="n">
         <v>29.2</v>
       </c>
-      <c r="U143" t="n">
+      <c r="V143" t="n">
         <v>52</v>
       </c>
-      <c r="V143" t="n">
-        <v>11</v>
-      </c>
       <c r="W143" t="n">
-        <v>1.617866621065988</v>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.8062745759725093</v>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11667,32 +12098,35 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q144" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R144" t="n">
+        <v>74</v>
+      </c>
+      <c r="S144" t="n">
         <v>28.6</v>
       </c>
-      <c r="S144" t="n">
+      <c r="T144" t="n">
         <v>34</v>
       </c>
-      <c r="T144" t="n">
+      <c r="U144" t="n">
         <v>29.2</v>
       </c>
-      <c r="U144" t="n">
+      <c r="V144" t="n">
         <v>52</v>
       </c>
-      <c r="V144" t="n">
-        <v>11</v>
-      </c>
       <c r="W144" t="n">
-        <v>1.813154701346886</v>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0.8319161249066052</v>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11745,30 +12179,33 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>91.2</v>
+        <v>76</v>
       </c>
       <c r="Q145" t="n">
-        <v>16.5</v>
+        <v>71</v>
       </c>
       <c r="R145" t="n">
+        <v>74</v>
+      </c>
+      <c r="S145" t="n">
         <v>27.8</v>
       </c>
-      <c r="S145" t="n">
+      <c r="T145" t="n">
         <v>33.2</v>
       </c>
-      <c r="T145" t="n">
+      <c r="U145" t="n">
         <v>29.2</v>
       </c>
-      <c r="U145" t="n">
+      <c r="V145" t="n">
         <v>52</v>
       </c>
-      <c r="V145" t="n">
-        <v>11</v>
-      </c>
       <c r="W145" t="n">
-        <v>1.950453190694078</v>
-      </c>
-      <c r="X145" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0.8679785727287234</v>
+      </c>
+      <c r="Y145" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -11823,30 +12260,33 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>90.8</v>
+        <v>76</v>
       </c>
       <c r="Q146" t="n">
-        <v>16.98</v>
+        <v>71</v>
       </c>
       <c r="R146" t="n">
+        <v>74</v>
+      </c>
+      <c r="S146" t="n">
         <v>27.6</v>
       </c>
-      <c r="S146" t="n">
+      <c r="T146" t="n">
         <v>33</v>
       </c>
-      <c r="T146" t="n">
+      <c r="U146" t="n">
         <v>29.4</v>
       </c>
-      <c r="U146" t="n">
+      <c r="V146" t="n">
         <v>51.8</v>
       </c>
-      <c r="V146" t="n">
-        <v>11</v>
-      </c>
       <c r="W146" t="n">
-        <v>1.896354559090749</v>
-      </c>
-      <c r="X146" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0.8695638379073061</v>
+      </c>
+      <c r="Y146" t="inlineStr">
         <is>
           <t>Observation Required (Pattern Change)</t>
         </is>
@@ -11901,32 +12341,35 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>93.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q147" t="n">
-        <v>16.72</v>
+        <v>71</v>
       </c>
       <c r="R147" t="n">
+        <v>74</v>
+      </c>
+      <c r="S147" t="n">
         <v>28</v>
       </c>
-      <c r="S147" t="n">
+      <c r="T147" t="n">
         <v>34</v>
       </c>
-      <c r="T147" t="n">
+      <c r="U147" t="n">
         <v>29.8</v>
       </c>
-      <c r="U147" t="n">
+      <c r="V147" t="n">
         <v>51.6</v>
       </c>
-      <c r="V147" t="n">
-        <v>11</v>
-      </c>
       <c r="W147" t="n">
-        <v>1.831448042175761</v>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0.8119115189718004</v>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -11979,32 +12422,35 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>95.8</v>
+        <v>76</v>
       </c>
       <c r="Q148" t="n">
-        <v>16.18</v>
+        <v>71</v>
       </c>
       <c r="R148" t="n">
+        <v>74</v>
+      </c>
+      <c r="S148" t="n">
         <v>29</v>
       </c>
-      <c r="S148" t="n">
+      <c r="T148" t="n">
         <v>35</v>
       </c>
-      <c r="T148" t="n">
+      <c r="U148" t="n">
         <v>30.2</v>
       </c>
-      <c r="U148" t="n">
+      <c r="V148" t="n">
         <v>51.4</v>
       </c>
-      <c r="V148" t="n">
-        <v>11</v>
-      </c>
       <c r="W148" t="n">
-        <v>1.925646301842964</v>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0.7586372075091657</v>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12057,32 +12503,35 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>100.4</v>
+        <v>76</v>
       </c>
       <c r="Q149" t="n">
-        <v>15.58</v>
+        <v>71</v>
       </c>
       <c r="R149" t="n">
+        <v>74</v>
+      </c>
+      <c r="S149" t="n">
         <v>30.2</v>
       </c>
-      <c r="S149" t="n">
+      <c r="T149" t="n">
         <v>35.8</v>
       </c>
-      <c r="T149" t="n">
+      <c r="U149" t="n">
         <v>30.6</v>
       </c>
-      <c r="U149" t="n">
+      <c r="V149" t="n">
         <v>51.2</v>
       </c>
-      <c r="V149" t="n">
-        <v>11</v>
-      </c>
       <c r="W149" t="n">
-        <v>2.290749968193132</v>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X149" t="n">
+        <v>0.7239821150210852</v>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12135,32 +12584,35 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>102.8</v>
+        <v>76</v>
       </c>
       <c r="Q150" t="n">
-        <v>14.26</v>
+        <v>71</v>
       </c>
       <c r="R150" t="n">
+        <v>74</v>
+      </c>
+      <c r="S150" t="n">
         <v>31.2</v>
       </c>
-      <c r="S150" t="n">
+      <c r="T150" t="n">
         <v>36.6</v>
       </c>
-      <c r="T150" t="n">
+      <c r="U150" t="n">
         <v>30.8</v>
       </c>
-      <c r="U150" t="n">
+      <c r="V150" t="n">
         <v>51.4</v>
       </c>
-      <c r="V150" t="n">
-        <v>11</v>
-      </c>
       <c r="W150" t="n">
-        <v>2.700789470167989</v>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0.7067591078266303</v>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12213,32 +12665,35 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q151" t="n">
-        <v>14.26</v>
+        <v>71</v>
       </c>
       <c r="R151" t="n">
+        <v>74</v>
+      </c>
+      <c r="S151" t="n">
         <v>31</v>
       </c>
-      <c r="S151" t="n">
+      <c r="T151" t="n">
         <v>36.4</v>
       </c>
-      <c r="T151" t="n">
+      <c r="U151" t="n">
         <v>30.6</v>
       </c>
-      <c r="U151" t="n">
+      <c r="V151" t="n">
         <v>51.8</v>
       </c>
-      <c r="V151" t="n">
-        <v>11</v>
-      </c>
       <c r="W151" t="n">
-        <v>2.582259749363864</v>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0.7036366580790984</v>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12291,32 +12746,35 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>99.8</v>
+        <v>76</v>
       </c>
       <c r="Q152" t="n">
-        <v>15.66</v>
+        <v>71</v>
       </c>
       <c r="R152" t="n">
+        <v>74</v>
+      </c>
+      <c r="S152" t="n">
         <v>31</v>
       </c>
-      <c r="S152" t="n">
+      <c r="T152" t="n">
         <v>36.2</v>
       </c>
-      <c r="T152" t="n">
+      <c r="U152" t="n">
         <v>30.6</v>
       </c>
-      <c r="U152" t="n">
+      <c r="V152" t="n">
         <v>52</v>
       </c>
-      <c r="V152" t="n">
-        <v>11</v>
-      </c>
       <c r="W152" t="n">
-        <v>2.219039031273183</v>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0.6965114001947531</v>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12369,32 +12827,35 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>99.2</v>
+        <v>76</v>
       </c>
       <c r="Q153" t="n">
-        <v>16.5</v>
+        <v>71</v>
       </c>
       <c r="R153" t="n">
+        <v>74</v>
+      </c>
+      <c r="S153" t="n">
         <v>31.2</v>
       </c>
-      <c r="S153" t="n">
+      <c r="T153" t="n">
         <v>36.4</v>
       </c>
-      <c r="T153" t="n">
+      <c r="U153" t="n">
         <v>30.6</v>
       </c>
-      <c r="U153" t="n">
+      <c r="V153" t="n">
         <v>52</v>
       </c>
-      <c r="V153" t="n">
-        <v>11</v>
-      </c>
       <c r="W153" t="n">
-        <v>2.04644277640877</v>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0.6974390132539976</v>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12447,32 +12908,35 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>98.2</v>
+        <v>76</v>
       </c>
       <c r="Q154" t="n">
-        <v>17.3</v>
+        <v>71</v>
       </c>
       <c r="R154" t="n">
+        <v>74</v>
+      </c>
+      <c r="S154" t="n">
         <v>31</v>
       </c>
-      <c r="S154" t="n">
+      <c r="T154" t="n">
         <v>36.8</v>
       </c>
-      <c r="T154" t="n">
+      <c r="U154" t="n">
         <v>30.8</v>
       </c>
-      <c r="U154" t="n">
+      <c r="V154" t="n">
         <v>52.2</v>
       </c>
-      <c r="V154" t="n">
-        <v>11</v>
-      </c>
       <c r="W154" t="n">
-        <v>1.846657059915636</v>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0.6878031100752376</v>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12989,35 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q155" t="n">
-        <v>17.52</v>
+        <v>71</v>
       </c>
       <c r="R155" t="n">
+        <v>74</v>
+      </c>
+      <c r="S155" t="n">
         <v>31</v>
       </c>
-      <c r="S155" t="n">
+      <c r="T155" t="n">
         <v>37.2</v>
       </c>
-      <c r="T155" t="n">
+      <c r="U155" t="n">
         <v>31.2</v>
       </c>
-      <c r="U155" t="n">
+      <c r="V155" t="n">
         <v>52</v>
       </c>
-      <c r="V155" t="n">
-        <v>11</v>
-      </c>
       <c r="W155" t="n">
-        <v>1.782883974166946</v>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0.6823777756573821</v>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12603,32 +13070,35 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>97.8</v>
+        <v>76</v>
       </c>
       <c r="Q156" t="n">
-        <v>18.04</v>
+        <v>71</v>
       </c>
       <c r="R156" t="n">
+        <v>74</v>
+      </c>
+      <c r="S156" t="n">
         <v>30.8</v>
       </c>
-      <c r="S156" t="n">
+      <c r="T156" t="n">
         <v>37.6</v>
       </c>
-      <c r="T156" t="n">
+      <c r="U156" t="n">
         <v>31.4</v>
       </c>
-      <c r="U156" t="n">
+      <c r="V156" t="n">
         <v>51.8</v>
       </c>
-      <c r="V156" t="n">
-        <v>11</v>
-      </c>
       <c r="W156" t="n">
-        <v>1.707429787260772</v>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0.6914398106847907</v>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12681,32 +13151,35 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>96.8</v>
+        <v>76</v>
       </c>
       <c r="Q157" t="n">
-        <v>18.3</v>
+        <v>71</v>
       </c>
       <c r="R157" t="n">
+        <v>74</v>
+      </c>
+      <c r="S157" t="n">
         <v>30.8</v>
       </c>
-      <c r="S157" t="n">
+      <c r="T157" t="n">
         <v>38</v>
       </c>
-      <c r="T157" t="n">
+      <c r="U157" t="n">
         <v>31.2</v>
       </c>
-      <c r="U157" t="n">
+      <c r="V157" t="n">
         <v>51.8</v>
       </c>
-      <c r="V157" t="n">
-        <v>11</v>
-      </c>
       <c r="W157" t="n">
-        <v>1.612171038096809</v>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0.7117574545614251</v>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12759,32 +13232,35 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q158" t="n">
-        <v>18.48</v>
+        <v>71</v>
       </c>
       <c r="R158" t="n">
+        <v>74</v>
+      </c>
+      <c r="S158" t="n">
         <v>30.8</v>
       </c>
-      <c r="S158" t="n">
+      <c r="T158" t="n">
         <v>38</v>
       </c>
-      <c r="T158" t="n">
+      <c r="U158" t="n">
         <v>31.2</v>
       </c>
-      <c r="U158" t="n">
+      <c r="V158" t="n">
         <v>52.2</v>
       </c>
-      <c r="V158" t="n">
-        <v>11</v>
-      </c>
       <c r="W158" t="n">
-        <v>1.568618833913904</v>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0.7012963494667102</v>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12837,32 +13313,35 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>95.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q159" t="n">
-        <v>18.5</v>
+        <v>71</v>
       </c>
       <c r="R159" t="n">
+        <v>74</v>
+      </c>
+      <c r="S159" t="n">
         <v>31</v>
       </c>
-      <c r="S159" t="n">
+      <c r="T159" t="n">
         <v>37.8</v>
       </c>
-      <c r="T159" t="n">
+      <c r="U159" t="n">
         <v>30.8</v>
       </c>
-      <c r="U159" t="n">
+      <c r="V159" t="n">
         <v>52.2</v>
       </c>
-      <c r="V159" t="n">
-        <v>11</v>
-      </c>
       <c r="W159" t="n">
-        <v>1.52569796124819</v>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X159" t="n">
+        <v>0.7116738411517138</v>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12915,32 +13394,35 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q160" t="n">
-        <v>18.6</v>
+        <v>71</v>
       </c>
       <c r="R160" t="n">
+        <v>74</v>
+      </c>
+      <c r="S160" t="n">
         <v>30.4</v>
       </c>
-      <c r="S160" t="n">
+      <c r="T160" t="n">
         <v>36.8</v>
       </c>
-      <c r="T160" t="n">
+      <c r="U160" t="n">
         <v>30.4</v>
       </c>
-      <c r="U160" t="n">
+      <c r="V160" t="n">
         <v>52.2</v>
       </c>
-      <c r="V160" t="n">
-        <v>-1</v>
-      </c>
       <c r="W160" t="n">
-        <v>3</v>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X160" t="n">
+        <v>0.7131115696637392</v>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -12993,32 +13475,35 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q161" t="n">
-        <v>17.08</v>
+        <v>71</v>
       </c>
       <c r="R161" t="n">
+        <v>74</v>
+      </c>
+      <c r="S161" t="n">
         <v>30</v>
       </c>
-      <c r="S161" t="n">
+      <c r="T161" t="n">
         <v>35.8</v>
       </c>
-      <c r="T161" t="n">
+      <c r="U161" t="n">
         <v>30</v>
       </c>
-      <c r="U161" t="n">
+      <c r="V161" t="n">
         <v>52</v>
       </c>
-      <c r="V161" t="n">
-        <v>-1</v>
-      </c>
       <c r="W161" t="n">
-        <v>3</v>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0.7378204973228836</v>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13071,32 +13556,35 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>78.2</v>
+        <v>76</v>
       </c>
       <c r="Q162" t="n">
-        <v>16.78</v>
+        <v>71</v>
       </c>
       <c r="R162" t="n">
+        <v>74</v>
+      </c>
+      <c r="S162" t="n">
         <v>30</v>
       </c>
-      <c r="S162" t="n">
+      <c r="T162" t="n">
         <v>35.6</v>
       </c>
-      <c r="T162" t="n">
+      <c r="U162" t="n">
         <v>29.8</v>
       </c>
-      <c r="U162" t="n">
+      <c r="V162" t="n">
         <v>58</v>
       </c>
-      <c r="V162" t="n">
-        <v>-1</v>
-      </c>
       <c r="W162" t="n">
-        <v>3</v>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0.7524715828223622</v>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13149,32 +13637,35 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>78.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q163" t="n">
-        <v>17.78</v>
+        <v>71</v>
       </c>
       <c r="R163" t="n">
+        <v>74</v>
+      </c>
+      <c r="S163" t="n">
         <v>29.8</v>
       </c>
-      <c r="S163" t="n">
+      <c r="T163" t="n">
         <v>35.4</v>
       </c>
-      <c r="T163" t="n">
+      <c r="U163" t="n">
         <v>29.4</v>
       </c>
-      <c r="U163" t="n">
+      <c r="V163" t="n">
         <v>58</v>
       </c>
-      <c r="V163" t="n">
-        <v>-1</v>
-      </c>
       <c r="W163" t="n">
-        <v>3</v>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0.7830348972767927</v>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13227,32 +13718,35 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>79.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q164" t="n">
-        <v>18.26</v>
+        <v>71</v>
       </c>
       <c r="R164" t="n">
+        <v>74</v>
+      </c>
+      <c r="S164" t="n">
         <v>30.2</v>
       </c>
-      <c r="S164" t="n">
+      <c r="T164" t="n">
         <v>36</v>
       </c>
-      <c r="T164" t="n">
+      <c r="U164" t="n">
         <v>29.6</v>
       </c>
-      <c r="U164" t="n">
+      <c r="V164" t="n">
         <v>58</v>
       </c>
-      <c r="V164" t="n">
-        <v>-1</v>
-      </c>
       <c r="W164" t="n">
-        <v>3</v>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0.764561492089412</v>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13305,32 +13799,35 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>98.8</v>
+        <v>76</v>
       </c>
       <c r="Q165" t="n">
-        <v>18.78</v>
+        <v>71</v>
       </c>
       <c r="R165" t="n">
+        <v>74</v>
+      </c>
+      <c r="S165" t="n">
         <v>31.2</v>
       </c>
-      <c r="S165" t="n">
+      <c r="T165" t="n">
         <v>37</v>
       </c>
-      <c r="T165" t="n">
+      <c r="U165" t="n">
         <v>29.4</v>
       </c>
-      <c r="U165" t="n">
+      <c r="V165" t="n">
         <v>57.8</v>
       </c>
-      <c r="V165" t="n">
-        <v>-1</v>
-      </c>
       <c r="W165" t="n">
-        <v>3</v>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X165" t="n">
+        <v>0.7789072130624978</v>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13383,32 +13880,35 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>101.4</v>
+        <v>76</v>
       </c>
       <c r="Q166" t="n">
-        <v>18.68</v>
+        <v>71</v>
       </c>
       <c r="R166" t="n">
+        <v>74</v>
+      </c>
+      <c r="S166" t="n">
         <v>32.2</v>
       </c>
-      <c r="S166" t="n">
+      <c r="T166" t="n">
         <v>38</v>
       </c>
-      <c r="T166" t="n">
+      <c r="U166" t="n">
         <v>29.6</v>
       </c>
-      <c r="U166" t="n">
+      <c r="V166" t="n">
         <v>57.8</v>
       </c>
-      <c r="V166" t="n">
-        <v>-1</v>
-      </c>
       <c r="W166" t="n">
-        <v>3</v>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X166" t="n">
+        <v>0.7888615160943856</v>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13461,32 +13961,35 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q167" t="n">
-        <v>16.92</v>
+        <v>71</v>
       </c>
       <c r="R167" t="n">
+        <v>74</v>
+      </c>
+      <c r="S167" t="n">
         <v>32.6</v>
       </c>
-      <c r="S167" t="n">
+      <c r="T167" t="n">
         <v>37.8</v>
       </c>
-      <c r="T167" t="n">
+      <c r="U167" t="n">
         <v>29.8</v>
       </c>
-      <c r="U167" t="n">
+      <c r="V167" t="n">
         <v>51.4</v>
       </c>
-      <c r="V167" t="n">
-        <v>11</v>
-      </c>
       <c r="W167" t="n">
-        <v>2.335665467632778</v>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X167" t="n">
+        <v>0.7900595950849083</v>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13539,32 +14042,35 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>102.8</v>
+        <v>76</v>
       </c>
       <c r="Q168" t="n">
-        <v>16.62</v>
+        <v>71</v>
       </c>
       <c r="R168" t="n">
+        <v>74</v>
+      </c>
+      <c r="S168" t="n">
         <v>32.2</v>
       </c>
-      <c r="S168" t="n">
+      <c r="T168" t="n">
         <v>37.8</v>
       </c>
-      <c r="T168" t="n">
+      <c r="U168" t="n">
         <v>30</v>
       </c>
-      <c r="U168" t="n">
+      <c r="V168" t="n">
         <v>50.8</v>
       </c>
-      <c r="V168" t="n">
-        <v>11</v>
-      </c>
       <c r="W168" t="n">
-        <v>2.41988200183725</v>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0.7945357937236257</v>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13617,32 +14123,35 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>102.2</v>
+        <v>76</v>
       </c>
       <c r="Q169" t="n">
-        <v>17.52</v>
+        <v>71</v>
       </c>
       <c r="R169" t="n">
+        <v>74</v>
+      </c>
+      <c r="S169" t="n">
         <v>31.6</v>
       </c>
-      <c r="S169" t="n">
+      <c r="T169" t="n">
         <v>37.2</v>
       </c>
-      <c r="T169" t="n">
+      <c r="U169" t="n">
         <v>29.8</v>
       </c>
-      <c r="U169" t="n">
+      <c r="V169" t="n">
         <v>50.4</v>
       </c>
-      <c r="V169" t="n">
-        <v>11</v>
-      </c>
       <c r="W169" t="n">
-        <v>2.244415503384954</v>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0.8055839886035697</v>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13695,32 +14204,35 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q170" t="n">
-        <v>17.96</v>
+        <v>71</v>
       </c>
       <c r="R170" t="n">
+        <v>74</v>
+      </c>
+      <c r="S170" t="n">
         <v>31.6</v>
       </c>
-      <c r="S170" t="n">
+      <c r="T170" t="n">
         <v>37.8</v>
       </c>
-      <c r="T170" t="n">
+      <c r="U170" t="n">
         <v>30</v>
       </c>
-      <c r="U170" t="n">
+      <c r="V170" t="n">
         <v>50.4</v>
       </c>
-      <c r="V170" t="n">
-        <v>11</v>
-      </c>
       <c r="W170" t="n">
-        <v>2.12281033671983</v>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X170" t="n">
+        <v>0.8075378390913216</v>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13773,32 +14285,35 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>101.2</v>
+        <v>76</v>
       </c>
       <c r="Q171" t="n">
-        <v>18.4</v>
+        <v>71</v>
       </c>
       <c r="R171" t="n">
+        <v>74</v>
+      </c>
+      <c r="S171" t="n">
         <v>31.6</v>
       </c>
-      <c r="S171" t="n">
+      <c r="T171" t="n">
         <v>38.4</v>
       </c>
-      <c r="T171" t="n">
+      <c r="U171" t="n">
         <v>30</v>
       </c>
-      <c r="U171" t="n">
+      <c r="V171" t="n">
         <v>50.4</v>
       </c>
-      <c r="V171" t="n">
-        <v>11</v>
-      </c>
       <c r="W171" t="n">
-        <v>2.031286185329141</v>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X171" t="n">
+        <v>0.8261890470200454</v>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13851,32 +14366,35 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>101.6</v>
+        <v>76</v>
       </c>
       <c r="Q172" t="n">
-        <v>18.1</v>
+        <v>71</v>
       </c>
       <c r="R172" t="n">
+        <v>74</v>
+      </c>
+      <c r="S172" t="n">
         <v>31.4</v>
       </c>
-      <c r="S172" t="n">
+      <c r="T172" t="n">
         <v>38.4</v>
       </c>
-      <c r="T172" t="n">
+      <c r="U172" t="n">
         <v>30</v>
       </c>
-      <c r="U172" t="n">
+      <c r="V172" t="n">
         <v>50.8</v>
       </c>
-      <c r="V172" t="n">
-        <v>11</v>
-      </c>
       <c r="W172" t="n">
-        <v>2.107920508559073</v>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X172" t="n">
+        <v>0.8131500987117997</v>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -13929,32 +14447,35 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>100.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q173" t="n">
-        <v>16</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R173" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S173" t="n">
         <v>40.8</v>
       </c>
-      <c r="S173" t="n">
+      <c r="T173" t="n">
         <v>46</v>
       </c>
-      <c r="T173" t="n">
+      <c r="U173" t="n">
         <v>34</v>
       </c>
-      <c r="U173" t="n">
+      <c r="V173" t="n">
         <v>66.2</v>
       </c>
-      <c r="V173" t="n">
-        <v>-1</v>
-      </c>
       <c r="W173" t="n">
-        <v>3</v>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>22</v>
+      </c>
+      <c r="X173" t="n">
+        <v>0.09228537254563066</v>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14007,32 +14528,35 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>101.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>15.14</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R174" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S174" t="n">
         <v>41.4</v>
       </c>
-      <c r="S174" t="n">
+      <c r="T174" t="n">
         <v>46</v>
       </c>
-      <c r="T174" t="n">
+      <c r="U174" t="n">
         <v>34.2</v>
       </c>
-      <c r="U174" t="n">
+      <c r="V174" t="n">
         <v>66.8</v>
       </c>
-      <c r="V174" t="n">
-        <v>-1</v>
-      </c>
       <c r="W174" t="n">
-        <v>3</v>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>22</v>
+      </c>
+      <c r="X174" t="n">
+        <v>0.05615007180954815</v>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14085,32 +14609,35 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>100.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q175" t="n">
-        <v>15.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R175" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S175" t="n">
         <v>41.6</v>
       </c>
-      <c r="S175" t="n">
+      <c r="T175" t="n">
         <v>45.4</v>
       </c>
-      <c r="T175" t="n">
+      <c r="U175" t="n">
         <v>34.4</v>
       </c>
-      <c r="U175" t="n">
+      <c r="V175" t="n">
         <v>67.2</v>
       </c>
-      <c r="V175" t="n">
-        <v>-1</v>
-      </c>
       <c r="W175" t="n">
-        <v>3</v>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>22</v>
+      </c>
+      <c r="X175" t="n">
+        <v>0.0333300405968139</v>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14163,32 +14690,35 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>100.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q176" t="n">
-        <v>15.86</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R176" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S176" t="n">
         <v>41.6</v>
       </c>
-      <c r="S176" t="n">
+      <c r="T176" t="n">
         <v>44.8</v>
       </c>
-      <c r="T176" t="n">
+      <c r="U176" t="n">
         <v>34.4</v>
       </c>
-      <c r="U176" t="n">
+      <c r="V176" t="n">
         <v>67.2</v>
       </c>
-      <c r="V176" t="n">
-        <v>-1</v>
-      </c>
       <c r="W176" t="n">
-        <v>3</v>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>22</v>
+      </c>
+      <c r="X176" t="n">
+        <v>0.07787004378974678</v>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14241,32 +14771,35 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>100.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q177" t="n">
-        <v>16.36</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="R177" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S177" t="n">
         <v>41.2</v>
       </c>
-      <c r="S177" t="n">
+      <c r="T177" t="n">
         <v>45.2</v>
       </c>
-      <c r="T177" t="n">
+      <c r="U177" t="n">
         <v>34.4</v>
       </c>
-      <c r="U177" t="n">
+      <c r="V177" t="n">
         <v>67.2</v>
       </c>
-      <c r="V177" t="n">
-        <v>-1</v>
-      </c>
       <c r="W177" t="n">
-        <v>3</v>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>22</v>
+      </c>
+      <c r="X177" t="n">
+        <v>0.04028929367971716</v>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14319,32 +14852,35 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>102.6</v>
+        <v>76</v>
       </c>
       <c r="Q178" t="n">
-        <v>16.76</v>
+        <v>71</v>
       </c>
       <c r="R178" t="n">
+        <v>74</v>
+      </c>
+      <c r="S178" t="n">
         <v>32</v>
       </c>
-      <c r="S178" t="n">
+      <c r="T178" t="n">
         <v>37.8</v>
       </c>
-      <c r="T178" t="n">
+      <c r="U178" t="n">
         <v>30.4</v>
       </c>
-      <c r="U178" t="n">
+      <c r="V178" t="n">
         <v>52.2</v>
       </c>
-      <c r="V178" t="n">
-        <v>11</v>
-      </c>
       <c r="W178" t="n">
-        <v>2.359615400766875</v>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X178" t="n">
+        <v>0.7313917461427738</v>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14397,32 +14933,35 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q179" t="n">
-        <v>16.96</v>
+        <v>71</v>
       </c>
       <c r="R179" t="n">
+        <v>74</v>
+      </c>
+      <c r="S179" t="n">
         <v>32</v>
       </c>
-      <c r="S179" t="n">
+      <c r="T179" t="n">
         <v>38</v>
       </c>
-      <c r="T179" t="n">
+      <c r="U179" t="n">
         <v>30.4</v>
       </c>
-      <c r="U179" t="n">
+      <c r="V179" t="n">
         <v>52.2</v>
       </c>
-      <c r="V179" t="n">
-        <v>11</v>
-      </c>
       <c r="W179" t="n">
-        <v>2.313646228536225</v>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X179" t="n">
+        <v>0.7377140083976997</v>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14475,32 +15014,35 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q180" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R180" t="n">
+        <v>74</v>
+      </c>
+      <c r="S180" t="n">
         <v>31.8</v>
       </c>
-      <c r="S180" t="n">
+      <c r="T180" t="n">
         <v>38</v>
       </c>
-      <c r="T180" t="n">
+      <c r="U180" t="n">
         <v>30.4</v>
       </c>
-      <c r="U180" t="n">
+      <c r="V180" t="n">
         <v>52</v>
       </c>
-      <c r="V180" t="n">
-        <v>11</v>
-      </c>
       <c r="W180" t="n">
-        <v>2.297697618645537</v>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X180" t="n">
+        <v>0.7423338415908827</v>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14553,32 +15095,35 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q181" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R181" t="n">
+        <v>74</v>
+      </c>
+      <c r="S181" t="n">
         <v>32.4</v>
       </c>
-      <c r="S181" t="n">
+      <c r="T181" t="n">
         <v>38.2</v>
       </c>
-      <c r="T181" t="n">
+      <c r="U181" t="n">
         <v>30.4</v>
       </c>
-      <c r="U181" t="n">
+      <c r="V181" t="n">
         <v>52</v>
       </c>
-      <c r="V181" t="n">
-        <v>11</v>
-      </c>
       <c r="W181" t="n">
-        <v>2.300296362752592</v>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X181" t="n">
+        <v>0.7504280918066636</v>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14631,32 +15176,35 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q182" t="n">
-        <v>17.1</v>
+        <v>71</v>
       </c>
       <c r="R182" t="n">
+        <v>74</v>
+      </c>
+      <c r="S182" t="n">
         <v>32.8</v>
       </c>
-      <c r="S182" t="n">
+      <c r="T182" t="n">
         <v>38</v>
       </c>
-      <c r="T182" t="n">
+      <c r="U182" t="n">
         <v>30.4</v>
       </c>
-      <c r="U182" t="n">
+      <c r="V182" t="n">
         <v>51.6</v>
       </c>
-      <c r="V182" t="n">
-        <v>11</v>
-      </c>
       <c r="W182" t="n">
-        <v>2.302105280832317</v>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X182" t="n">
+        <v>0.7561293107648537</v>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14709,32 +15257,35 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>102.4</v>
+        <v>76</v>
       </c>
       <c r="Q183" t="n">
-        <v>16.78</v>
+        <v>71</v>
       </c>
       <c r="R183" t="n">
+        <v>74</v>
+      </c>
+      <c r="S183" t="n">
         <v>33.2</v>
       </c>
-      <c r="S183" t="n">
+      <c r="T183" t="n">
         <v>37.8</v>
       </c>
-      <c r="T183" t="n">
+      <c r="U183" t="n">
         <v>30.4</v>
       </c>
-      <c r="U183" t="n">
+      <c r="V183" t="n">
         <v>51.2</v>
       </c>
-      <c r="V183" t="n">
-        <v>11</v>
-      </c>
       <c r="W183" t="n">
-        <v>2.344627527621804</v>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X183" t="n">
+        <v>0.7645439457034146</v>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14787,32 +15338,35 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>103.8</v>
+        <v>76</v>
       </c>
       <c r="Q184" t="n">
-        <v>15.32</v>
+        <v>71</v>
       </c>
       <c r="R184" t="n">
+        <v>74</v>
+      </c>
+      <c r="S184" t="n">
         <v>33.4</v>
       </c>
-      <c r="S184" t="n">
+      <c r="T184" t="n">
         <v>37.2</v>
       </c>
-      <c r="T184" t="n">
+      <c r="U184" t="n">
         <v>30</v>
       </c>
-      <c r="U184" t="n">
+      <c r="V184" t="n">
         <v>50.8</v>
       </c>
-      <c r="V184" t="n">
-        <v>11</v>
-      </c>
       <c r="W184" t="n">
-        <v>2.693687537134263</v>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X184" t="n">
+        <v>0.7871260958589553</v>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14865,32 +15419,35 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="Q185" t="n">
-        <v>15.4</v>
+        <v>71</v>
       </c>
       <c r="R185" t="n">
+        <v>74</v>
+      </c>
+      <c r="S185" t="n">
         <v>32.6</v>
       </c>
-      <c r="S185" t="n">
+      <c r="T185" t="n">
         <v>36.6</v>
       </c>
-      <c r="T185" t="n">
+      <c r="U185" t="n">
         <v>30.4</v>
       </c>
-      <c r="U185" t="n">
+      <c r="V185" t="n">
         <v>52.8</v>
       </c>
-      <c r="V185" t="n">
-        <v>11</v>
-      </c>
       <c r="W185" t="n">
-        <v>2.460666294700433</v>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X185" t="n">
+        <v>0.6942238438710246</v>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -14943,32 +15500,35 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>99.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q186" t="n">
-        <v>15.22</v>
+        <v>71</v>
       </c>
       <c r="R186" t="n">
+        <v>74</v>
+      </c>
+      <c r="S186" t="n">
         <v>32.2</v>
       </c>
-      <c r="S186" t="n">
+      <c r="T186" t="n">
         <v>36.2</v>
       </c>
-      <c r="T186" t="n">
+      <c r="U186" t="n">
         <v>30.8</v>
       </c>
-      <c r="U186" t="n">
+      <c r="V186" t="n">
         <v>54.8</v>
       </c>
-      <c r="V186" t="n">
-        <v>11</v>
-      </c>
       <c r="W186" t="n">
-        <v>2.252976880108414</v>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X186" t="n">
+        <v>0.6439384754394504</v>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -15021,32 +15581,35 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>96.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q187" t="n">
-        <v>15.14</v>
+        <v>71</v>
       </c>
       <c r="R187" t="n">
+        <v>74</v>
+      </c>
+      <c r="S187" t="n">
         <v>31.8</v>
       </c>
-      <c r="S187" t="n">
+      <c r="T187" t="n">
         <v>36.2</v>
       </c>
-      <c r="T187" t="n">
+      <c r="U187" t="n">
         <v>30.8</v>
       </c>
-      <c r="U187" t="n">
+      <c r="V187" t="n">
         <v>56.4</v>
       </c>
-      <c r="V187" t="n">
-        <v>11</v>
-      </c>
       <c r="W187" t="n">
-        <v>2.086993871998955</v>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X187" t="n">
+        <v>0.6528373760148986</v>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -15099,32 +15662,35 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>93.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q188" t="n">
-        <v>15.02</v>
+        <v>70.8</v>
       </c>
       <c r="R188" t="n">
+        <v>74</v>
+      </c>
+      <c r="S188" t="n">
         <v>32.2</v>
       </c>
-      <c r="S188" t="n">
+      <c r="T188" t="n">
         <v>35.8</v>
       </c>
-      <c r="T188" t="n">
+      <c r="U188" t="n">
         <v>31</v>
       </c>
-      <c r="U188" t="n">
+      <c r="V188" t="n">
         <v>57.6</v>
       </c>
-      <c r="V188" t="n">
-        <v>11</v>
-      </c>
       <c r="W188" t="n">
-        <v>2.057660717990342</v>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Observation Required (Pattern Change)</t>
+        <v>16</v>
+      </c>
+      <c r="X188" t="n">
+        <v>0.7381032011852408</v>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -15177,32 +15743,35 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q189" t="n">
-        <v>14.78</v>
+        <v>70.8</v>
       </c>
       <c r="R189" t="n">
+        <v>74</v>
+      </c>
+      <c r="S189" t="n">
         <v>32.4</v>
       </c>
-      <c r="S189" t="n">
+      <c r="T189" t="n">
         <v>36</v>
       </c>
-      <c r="T189" t="n">
+      <c r="U189" t="n">
         <v>31.2</v>
       </c>
-      <c r="U189" t="n">
+      <c r="V189" t="n">
         <v>59</v>
       </c>
-      <c r="V189" t="n">
-        <v>-1</v>
-      </c>
       <c r="W189" t="n">
-        <v>3</v>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X189" t="n">
+        <v>0.7695795098737056</v>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -15255,32 +15824,35 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>92.2</v>
+        <v>76</v>
       </c>
       <c r="Q190" t="n">
-        <v>14.34</v>
+        <v>70.8</v>
       </c>
       <c r="R190" t="n">
+        <v>74</v>
+      </c>
+      <c r="S190" t="n">
         <v>33.8</v>
       </c>
-      <c r="S190" t="n">
+      <c r="T190" t="n">
         <v>36.2</v>
       </c>
-      <c r="T190" t="n">
+      <c r="U190" t="n">
         <v>30.6</v>
       </c>
-      <c r="U190" t="n">
+      <c r="V190" t="n">
         <v>58.2</v>
       </c>
-      <c r="V190" t="n">
-        <v>-1</v>
-      </c>
       <c r="W190" t="n">
-        <v>3</v>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X190" t="n">
+        <v>0.78344848408143</v>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>
@@ -15333,32 +15905,35 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>91.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="Q191" t="n">
-        <v>15.92</v>
+        <v>70.8</v>
       </c>
       <c r="R191" t="n">
+        <v>74</v>
+      </c>
+      <c r="S191" t="n">
         <v>33.8</v>
       </c>
-      <c r="S191" t="n">
+      <c r="T191" t="n">
         <v>36.4</v>
       </c>
-      <c r="T191" t="n">
+      <c r="U191" t="n">
         <v>30.6</v>
       </c>
-      <c r="U191" t="n">
+      <c r="V191" t="n">
         <v>58</v>
       </c>
-      <c r="V191" t="n">
-        <v>-1</v>
-      </c>
       <c r="W191" t="n">
-        <v>3</v>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Investigation Needed (Operational Drift)</t>
+        <v>16</v>
+      </c>
+      <c r="X191" t="n">
+        <v>0.7799684710610361</v>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Healthy (Optimal Performance)</t>
         </is>
       </c>
     </row>

--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output2.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_bearings_vibration_temp_clustering/clustering/dsas_g11_clustering_output2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,112 +433,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9343</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9344</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9357</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9368</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9369</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9370</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9408</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>RecordDate</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RecordTime</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358_smooth</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359_smooth</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360_smooth</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361_smooth</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Behavior_Cluster</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Degradation_Index</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Health_Status</t>
         </is>
@@ -569,10 +581,10 @@
       <c r="L2" t="n">
         <v>7.5</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>46115.86637731481</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -596,7 +608,7 @@
         <v>12</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2967977290084655</v>
+        <v>0.2967977290084646</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -641,10 +653,10 @@
       <c r="L3" t="n">
         <v>7.5</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>46116.02179398148</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -668,7 +680,7 @@
         <v>12</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2854449317091436</v>
+        <v>0.2854449317091426</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -713,10 +725,10 @@
       <c r="L4" t="n">
         <v>7.4</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>46116.19790509259</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -740,7 +752,7 @@
         <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3003380041725939</v>
+        <v>0.3003380041725929</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -785,10 +797,10 @@
       <c r="L5" t="n">
         <v>7.4</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -812,7 +824,7 @@
         <v>12</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3186182091891047</v>
+        <v>0.3186182091891037</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -857,10 +869,10 @@
       <c r="L6" t="n">
         <v>7.5</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -884,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3397392359853696</v>
+        <v>0.3397392359853686</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -929,10 +941,10 @@
       <c r="L7" t="n">
         <v>2.2</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -956,7 +968,7 @@
         <v>12</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3321591374674711</v>
+        <v>0.3321591374674701</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1001,10 +1013,10 @@
       <c r="L8" t="n">
         <v>2.2</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1028,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="U8" t="n">
-        <v>0.283834048361406</v>
+        <v>0.283834048361405</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1073,10 +1085,10 @@
       <c r="L9" t="n">
         <v>2.2</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="N9" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1100,7 +1112,7 @@
         <v>12</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2973401332747677</v>
+        <v>0.2973401332747667</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1145,10 +1157,10 @@
       <c r="L10" t="n">
         <v>7.2</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1172,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3233502379541853</v>
+        <v>0.3233502379541846</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1217,10 +1229,10 @@
       <c r="L11" t="n">
         <v>7.2</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="N11" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1244,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2513292982535778</v>
+        <v>0.2513292982535772</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1289,10 +1301,10 @@
       <c r="L12" t="n">
         <v>7.2</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1316,7 +1328,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1703081244653764</v>
+        <v>0.1703081244653763</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1361,10 +1373,10 @@
       <c r="L13" t="n">
         <v>7.5</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1388,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1224656498050484</v>
+        <v>0.1224656498050492</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1433,10 +1445,10 @@
       <c r="L14" t="n">
         <v>7.2</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N14" s="2" t="n">
         <v>46117</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1460,7 +1472,7 @@
         <v>12</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1872253617060151</v>
+        <v>0.1872253617060163</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1505,10 +1517,10 @@
       <c r="L15" t="n">
         <v>7.3</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <v>46118.0265625</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="N15" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1532,7 +1544,7 @@
         <v>12</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2458734928183197</v>
+        <v>0.2458734928183204</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1577,10 +1589,10 @@
       <c r="L16" t="n">
         <v>7.3</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="N16" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -1604,7 +1616,7 @@
         <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>0.192754000081725</v>
+        <v>0.1927540000817258</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1649,10 +1661,10 @@
       <c r="L17" t="n">
         <v>7.3</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="N17" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -1676,7 +1688,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1592871005203758</v>
+        <v>0.1592871005203765</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1721,10 +1733,10 @@
       <c r="L18" t="n">
         <v>7.6</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="N18" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -1748,7 +1760,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06795143793746927</v>
+        <v>0.06795143793746837</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1793,10 +1805,10 @@
       <c r="L19" t="n">
         <v>7.6</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="N19" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -1820,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1170793252204513</v>
+        <v>0.1170793252204498</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1865,10 +1877,10 @@
       <c r="L20" t="n">
         <v>7.4</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="N20" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -1892,7 +1904,7 @@
         <v>12</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1625427948864712</v>
+        <v>0.1625427948864699</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1937,10 +1949,10 @@
       <c r="L21" t="n">
         <v>7.4</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="N21" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -1964,7 +1976,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2390729097602778</v>
+        <v>0.2390729097602766</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2009,10 +2021,10 @@
       <c r="L22" t="n">
         <v>7.5</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N22" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -2036,7 +2048,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2932909090484587</v>
+        <v>0.2932909090484576</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2081,10 +2093,10 @@
       <c r="L23" t="n">
         <v>7.5</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="N23" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -2108,7 +2120,7 @@
         <v>12</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3204227666161988</v>
+        <v>0.3204227666161978</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2153,10 +2165,10 @@
       <c r="L24" t="n">
         <v>2.3</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="N24" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -2180,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5761642179129127</v>
+        <v>0.5761642179129117</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2225,10 +2237,10 @@
       <c r="L25" t="n">
         <v>2.3</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
-      <c r="N25" s="1" t="n">
+      <c r="N25" s="2" t="n">
         <v>46120</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -2252,7 +2264,7 @@
         <v>12</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4672697121520855</v>
+        <v>0.4672697121520843</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2297,10 +2309,10 @@
       <c r="L26" t="n">
         <v>5.9</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="N26" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -2324,7 +2336,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="n">
-        <v>0.292278351937633</v>
+        <v>0.2922783519376319</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2369,10 +2381,10 @@
       <c r="L27" t="n">
         <v>6.1</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
-      <c r="N27" s="1" t="n">
+      <c r="N27" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -2396,7 +2408,7 @@
         <v>12</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1863430617552625</v>
+        <v>0.1863430617552611</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2441,10 +2453,10 @@
       <c r="L28" t="n">
         <v>2.4</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
-      <c r="N28" s="1" t="n">
+      <c r="N28" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -2468,7 +2480,7 @@
         <v>12</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08394863360159528</v>
+        <v>0.08394863360159396</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2513,10 +2525,10 @@
       <c r="L29" t="n">
         <v>2.5</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
-      <c r="N29" s="1" t="n">
+      <c r="N29" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -2540,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3136071368406795</v>
+        <v>0.3136071368406804</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
       <c r="L30" t="n">
         <v>2.5</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
-      <c r="N30" s="1" t="n">
+      <c r="N30" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -2612,7 +2624,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3657994143230473</v>
+        <v>0.3657994143230482</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2657,10 +2669,10 @@
       <c r="L31" t="n">
         <v>6.3</v>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
-      <c r="N31" s="1" t="n">
+      <c r="N31" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -2684,7 +2696,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3448535186067145</v>
+        <v>0.3448535186067154</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2729,10 +2741,10 @@
       <c r="L32" t="n">
         <v>6.3</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
-      <c r="N32" s="1" t="n">
+      <c r="N32" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -2756,7 +2768,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="n">
-        <v>0.5094230339823733</v>
+        <v>0.5094230339823741</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2801,10 +2813,10 @@
       <c r="L33" t="n">
         <v>6.3</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
-      <c r="N33" s="1" t="n">
+      <c r="N33" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -2828,7 +2840,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="n">
-        <v>0.6036146896159359</v>
+        <v>0.6036146896159368</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2873,10 +2885,10 @@
       <c r="L34" t="n">
         <v>6.3</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
-      <c r="N34" s="1" t="n">
+      <c r="N34" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -2900,7 +2912,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="n">
-        <v>0.6122478976954021</v>
+        <v>0.6122478976954031</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -2945,10 +2957,10 @@
       <c r="L35" t="n">
         <v>6.2</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
-      <c r="N35" s="1" t="n">
+      <c r="N35" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -2972,7 +2984,7 @@
         <v>12</v>
       </c>
       <c r="U35" t="n">
-        <v>0.5898262818633813</v>
+        <v>0.5898262818633824</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3017,10 +3029,10 @@
       <c r="L36" t="n">
         <v>6.4</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
-      <c r="N36" s="1" t="n">
+      <c r="N36" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -3044,7 +3056,7 @@
         <v>12</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5720736230835681</v>
+        <v>0.5720736230835692</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3089,10 +3101,10 @@
       <c r="L37" t="n">
         <v>6.3</v>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
-      <c r="N37" s="1" t="n">
+      <c r="N37" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -3116,7 +3128,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>0.524816869371458</v>
+        <v>0.524816869371459</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3161,10 +3173,10 @@
       <c r="L38" t="n">
         <v>6.3</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
-      <c r="N38" s="1" t="n">
+      <c r="N38" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -3188,7 +3200,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="n">
-        <v>0.579677099872435</v>
+        <v>0.5796770998724361</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3233,10 +3245,10 @@
       <c r="L39" t="n">
         <v>6.5</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
-      <c r="N39" s="1" t="n">
+      <c r="N39" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -3260,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="U39" t="n">
-        <v>0.6605932811614779</v>
+        <v>0.6605932811614788</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3305,10 +3317,10 @@
       <c r="L40" t="n">
         <v>6.5</v>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
-      <c r="N40" s="1" t="n">
+      <c r="N40" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -3332,7 +3344,7 @@
         <v>12</v>
       </c>
       <c r="U40" t="n">
-        <v>0.7558253880319347</v>
+        <v>0.7558253880319357</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3377,10 +3389,10 @@
       <c r="L41" t="n">
         <v>6.5</v>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
-      <c r="N41" s="1" t="n">
+      <c r="N41" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -3404,7 +3416,7 @@
         <v>12</v>
       </c>
       <c r="U41" t="n">
-        <v>0.8369940128595842</v>
+        <v>0.8369940128595853</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3449,10 +3461,10 @@
       <c r="L42" t="n">
         <v>6.4</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
-      <c r="N42" s="1" t="n">
+      <c r="N42" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -3476,7 +3488,7 @@
         <v>12</v>
       </c>
       <c r="U42" t="n">
-        <v>0.7604705394882222</v>
+        <v>0.7604705394882232</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3521,10 +3533,10 @@
       <c r="L43" t="n">
         <v>2.5</v>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
-      <c r="N43" s="1" t="n">
+      <c r="N43" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -3548,7 +3560,7 @@
         <v>12</v>
       </c>
       <c r="U43" t="n">
-        <v>0.7379967722491846</v>
+        <v>0.7379967722491856</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -3593,10 +3605,10 @@
       <c r="L44" t="n">
         <v>2.4</v>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
-      <c r="N44" s="1" t="n">
+      <c r="N44" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -3620,7 +3632,7 @@
         <v>12</v>
       </c>
       <c r="U44" t="n">
-        <v>0.7729295453801533</v>
+        <v>0.7729295453801543</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3665,10 +3677,10 @@
       <c r="L45" t="n">
         <v>2.4</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
-      <c r="N45" s="1" t="n">
+      <c r="N45" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -3692,7 +3704,7 @@
         <v>12</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8470909551418188</v>
+        <v>0.8470909551418199</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3737,10 +3749,10 @@
       <c r="L46" t="n">
         <v>6.6</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
-      <c r="N46" s="1" t="n">
+      <c r="N46" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -3764,7 +3776,7 @@
         <v>12</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8712014074695815</v>
+        <v>0.8712014074695825</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -3809,10 +3821,10 @@
       <c r="L47" t="n">
         <v>6.7</v>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
-      <c r="N47" s="1" t="n">
+      <c r="N47" s="2" t="n">
         <v>46127</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -3836,7 +3848,7 @@
         <v>12</v>
       </c>
       <c r="U47" t="n">
-        <v>0.8955787642000169</v>
+        <v>0.8955787642000179</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -3881,10 +3893,10 @@
       <c r="L48" t="n">
         <v>6.6</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
-      <c r="N48" s="1" t="n">
+      <c r="N48" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -3908,7 +3920,7 @@
         <v>12</v>
       </c>
       <c r="U48" t="n">
-        <v>0.8389877107541627</v>
+        <v>0.8389877107541637</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -3953,10 +3965,10 @@
       <c r="L49" t="n">
         <v>6.6</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
-      <c r="N49" s="1" t="n">
+      <c r="N49" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -3980,7 +3992,7 @@
         <v>12</v>
       </c>
       <c r="U49" t="n">
-        <v>0.8504467178472099</v>
+        <v>0.8504467178472109</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4025,10 +4037,10 @@
       <c r="L50" t="n">
         <v>6.6</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="2" t="n">
         <v>46128.3578125</v>
       </c>
-      <c r="N50" s="1" t="n">
+      <c r="N50" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -4052,7 +4064,7 @@
         <v>12</v>
       </c>
       <c r="U50" t="n">
-        <v>0.797791432240706</v>
+        <v>0.7977914322407068</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4097,10 +4109,10 @@
       <c r="L51" t="n">
         <v>6.7</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
-      <c r="N51" s="1" t="n">
+      <c r="N51" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -4124,7 +4136,7 @@
         <v>12</v>
       </c>
       <c r="U51" t="n">
-        <v>0.8144718540440619</v>
+        <v>0.8144718540440626</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -4169,10 +4181,10 @@
       <c r="L52" t="n">
         <v>2.4</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
-      <c r="N52" s="1" t="n">
+      <c r="N52" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -4196,7 +4208,7 @@
         <v>12</v>
       </c>
       <c r="U52" t="n">
-        <v>0.9147838375799193</v>
+        <v>0.9147838375799202</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -4241,10 +4253,10 @@
       <c r="L53" t="n">
         <v>2.4</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
-      <c r="N53" s="1" t="n">
+      <c r="N53" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -4268,7 +4280,7 @@
         <v>12</v>
       </c>
       <c r="U53" t="n">
-        <v>0.966926742460594</v>
+        <v>0.9669267424605948</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4313,10 +4325,10 @@
       <c r="L54" t="n">
         <v>2.4</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
-      <c r="N54" s="1" t="n">
+      <c r="N54" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -4340,7 +4352,7 @@
         <v>12</v>
       </c>
       <c r="U54" t="n">
-        <v>0.9081898658008803</v>
+        <v>0.9081898658008811</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4385,10 +4397,10 @@
       <c r="L55" t="n">
         <v>6.8</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
-      <c r="N55" s="1" t="n">
+      <c r="N55" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -4412,7 +4424,7 @@
         <v>12</v>
       </c>
       <c r="U55" t="n">
-        <v>0.8903140701724405</v>
+        <v>0.8903140701724412</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -4457,10 +4469,10 @@
       <c r="L56" t="n">
         <v>6.7</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
-      <c r="N56" s="1" t="n">
+      <c r="N56" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -4484,7 +4496,7 @@
         <v>12</v>
       </c>
       <c r="U56" t="n">
-        <v>0.9283646439890847</v>
+        <v>0.9283646439890856</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -4529,10 +4541,10 @@
       <c r="L57" t="n">
         <v>6.7</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
-      <c r="N57" s="1" t="n">
+      <c r="N57" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -4556,7 +4568,7 @@
         <v>12</v>
       </c>
       <c r="U57" t="n">
-        <v>0.9418534480353462</v>
+        <v>0.9418534480353472</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -4601,10 +4613,10 @@
       <c r="L58" t="n">
         <v>6.7</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
-      <c r="N58" s="1" t="n">
+      <c r="N58" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -4628,7 +4640,7 @@
         <v>12</v>
       </c>
       <c r="U58" t="n">
-        <v>0.987767568672245</v>
+        <v>0.9877675686722459</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -4673,10 +4685,10 @@
       <c r="L59" t="n">
         <v>6.7</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
-      <c r="N59" s="1" t="n">
+      <c r="N59" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -4700,7 +4712,7 @@
         <v>12</v>
       </c>
       <c r="U59" t="n">
-        <v>1.011035507286737</v>
+        <v>1.011035507286739</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -4745,10 +4757,10 @@
       <c r="L60" t="n">
         <v>6.7</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
-      <c r="N60" s="1" t="n">
+      <c r="N60" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -4772,7 +4784,7 @@
         <v>12</v>
       </c>
       <c r="U60" t="n">
-        <v>1.040181143871429</v>
+        <v>1.04018114387143</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -4817,10 +4829,10 @@
       <c r="L61" t="n">
         <v>6.7</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
-      <c r="N61" s="1" t="n">
+      <c r="N61" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -4844,7 +4856,7 @@
         <v>12</v>
       </c>
       <c r="U61" t="n">
-        <v>1.001666832558017</v>
+        <v>1.001666832558018</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -4889,10 +4901,10 @@
       <c r="L62" t="n">
         <v>6.7</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="M62" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
-      <c r="N62" s="1" t="n">
+      <c r="N62" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -4916,7 +4928,7 @@
         <v>12</v>
       </c>
       <c r="U62" t="n">
-        <v>0.9884783875381657</v>
+        <v>0.9884783875381669</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -4961,10 +4973,10 @@
       <c r="L63" t="n">
         <v>6.7</v>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="M63" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
-      <c r="N63" s="1" t="n">
+      <c r="N63" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -4988,7 +5000,7 @@
         <v>12</v>
       </c>
       <c r="U63" t="n">
-        <v>0.9616627495214333</v>
+        <v>0.9616627495214345</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -5033,10 +5045,10 @@
       <c r="L64" t="n">
         <v>7</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="M64" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
-      <c r="N64" s="1" t="n">
+      <c r="N64" s="2" t="n">
         <v>46130</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -5060,7 +5072,7 @@
         <v>12</v>
       </c>
       <c r="U64" t="n">
-        <v>0.924049715210611</v>
+        <v>0.9240497152106122</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -5105,10 +5117,10 @@
       <c r="L65" t="n">
         <v>7</v>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="M65" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
-      <c r="N65" s="1" t="n">
+      <c r="N65" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -5132,7 +5144,7 @@
         <v>12</v>
       </c>
       <c r="U65" t="n">
-        <v>0.890328156770997</v>
+        <v>0.890328156770998</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -5177,10 +5189,10 @@
       <c r="L66" t="n">
         <v>2.4</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="M66" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
-      <c r="N66" s="1" t="n">
+      <c r="N66" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -5204,7 +5216,7 @@
         <v>12</v>
       </c>
       <c r="U66" t="n">
-        <v>0.8609554549989289</v>
+        <v>0.8609554549989299</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -5249,10 +5261,10 @@
       <c r="L67" t="n">
         <v>2.4</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M67" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
-      <c r="N67" s="1" t="n">
+      <c r="N67" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -5276,7 +5288,7 @@
         <v>12</v>
       </c>
       <c r="U67" t="n">
-        <v>0.9031323153791129</v>
+        <v>0.9031323153791139</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -5321,10 +5333,10 @@
       <c r="L68" t="n">
         <v>2.4</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M68" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
-      <c r="N68" s="1" t="n">
+      <c r="N68" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -5348,7 +5360,7 @@
         <v>12</v>
       </c>
       <c r="U68" t="n">
-        <v>0.9233405259461518</v>
+        <v>0.9233405259461528</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -5393,10 +5405,10 @@
       <c r="L69" t="n">
         <v>6.8</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M69" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
-      <c r="N69" s="1" t="n">
+      <c r="N69" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -5420,7 +5432,7 @@
         <v>12</v>
       </c>
       <c r="U69" t="n">
-        <v>0.9680441953361979</v>
+        <v>0.9680441953361989</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -5465,10 +5477,10 @@
       <c r="L70" t="n">
         <v>6.8</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M70" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="N70" s="2" t="n">
         <v>46131</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -5492,7 +5504,7 @@
         <v>12</v>
       </c>
       <c r="U70" t="n">
-        <v>0.9847556280767882</v>
+        <v>0.9847556280767892</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -5537,10 +5549,10 @@
       <c r="L71" t="n">
         <v>6.8</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M71" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="N71" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -5564,7 +5576,7 @@
         <v>12</v>
       </c>
       <c r="U71" t="n">
-        <v>1.042686477076075</v>
+        <v>1.042686477076076</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -5609,10 +5621,10 @@
       <c r="L72" t="n">
         <v>7</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M72" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="N72" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -5681,10 +5693,10 @@
       <c r="L73" t="n">
         <v>6.9</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M73" s="2" t="n">
         <v>46132.3584375</v>
       </c>
-      <c r="N73" s="1" t="n">
+      <c r="N73" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -5708,7 +5720,7 @@
         <v>12</v>
       </c>
       <c r="U73" t="n">
-        <v>1.026203152156364</v>
+        <v>1.026203152156365</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -5753,10 +5765,10 @@
       <c r="L74" t="n">
         <v>6.9</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M74" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="N74" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -5825,10 +5837,10 @@
       <c r="L75" t="n">
         <v>2.8</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M75" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="N75" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -5852,7 +5864,7 @@
         <v>12</v>
       </c>
       <c r="U75" t="n">
-        <v>1.02828040242158</v>
+        <v>1.028280402421581</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -5897,10 +5909,10 @@
       <c r="L76" t="n">
         <v>2.5</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M76" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="N76" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -5924,7 +5936,7 @@
         <v>12</v>
       </c>
       <c r="U76" t="n">
-        <v>0.9654644874851572</v>
+        <v>0.9654644874851581</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -5969,10 +5981,10 @@
       <c r="L77" t="n">
         <v>2.5</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M77" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
-      <c r="N77" s="1" t="n">
+      <c r="N77" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -5996,7 +6008,7 @@
         <v>12</v>
       </c>
       <c r="U77" t="n">
-        <v>0.903694794575901</v>
+        <v>0.903694794575902</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -6041,10 +6053,10 @@
       <c r="L78" t="n">
         <v>7</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M78" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="N78" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -6068,7 +6080,7 @@
         <v>12</v>
       </c>
       <c r="U78" t="n">
-        <v>0.9120838602388837</v>
+        <v>0.9120838602388847</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6113,10 +6125,10 @@
       <c r="L79" t="n">
         <v>7</v>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="M79" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
-      <c r="N79" s="1" t="n">
+      <c r="N79" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -6140,7 +6152,7 @@
         <v>12</v>
       </c>
       <c r="U79" t="n">
-        <v>0.8882414752407893</v>
+        <v>0.8882414752407903</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -6185,10 +6197,10 @@
       <c r="L80" t="n">
         <v>7</v>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="M80" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
-      <c r="N80" s="1" t="n">
+      <c r="N80" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -6212,7 +6224,7 @@
         <v>12</v>
       </c>
       <c r="U80" t="n">
-        <v>0.8623769035866584</v>
+        <v>0.8623769035866592</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6257,10 +6269,10 @@
       <c r="L81" t="n">
         <v>7</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="M81" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
-      <c r="N81" s="1" t="n">
+      <c r="N81" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -6284,7 +6296,7 @@
         <v>12</v>
       </c>
       <c r="U81" t="n">
-        <v>0.8796702297365624</v>
+        <v>0.8796702297365633</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -6329,10 +6341,10 @@
       <c r="L82" t="n">
         <v>7</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="M82" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
-      <c r="N82" s="1" t="n">
+      <c r="N82" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -6356,7 +6368,7 @@
         <v>12</v>
       </c>
       <c r="U82" t="n">
-        <v>0.8706658928397076</v>
+        <v>0.8706658928397084</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -6401,10 +6413,10 @@
       <c r="L83" t="n">
         <v>7</v>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="M83" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
-      <c r="N83" s="1" t="n">
+      <c r="N83" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -6428,7 +6440,7 @@
         <v>12</v>
       </c>
       <c r="U83" t="n">
-        <v>0.7932843974345329</v>
+        <v>0.7932843974345336</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -6473,10 +6485,10 @@
       <c r="L84" t="n">
         <v>6.9</v>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="M84" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
-      <c r="N84" s="1" t="n">
+      <c r="N84" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -6500,7 +6512,7 @@
         <v>12</v>
       </c>
       <c r="U84" t="n">
-        <v>0.833632398264186</v>
+        <v>0.8336323982641868</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -6545,10 +6557,10 @@
       <c r="L85" t="n">
         <v>6.9</v>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="M85" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
-      <c r="N85" s="1" t="n">
+      <c r="N85" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -6572,7 +6584,7 @@
         <v>12</v>
       </c>
       <c r="U85" t="n">
-        <v>0.9045737785454234</v>
+        <v>0.9045737785454243</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -6617,10 +6629,10 @@
       <c r="L86" t="n">
         <v>6.9</v>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="M86" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
-      <c r="N86" s="1" t="n">
+      <c r="N86" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -6644,7 +6656,7 @@
         <v>12</v>
       </c>
       <c r="U86" t="n">
-        <v>0.9769047077670957</v>
+        <v>0.9769047077670966</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -6689,10 +6701,10 @@
       <c r="L87" t="n">
         <v>7</v>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="M87" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
-      <c r="N87" s="1" t="n">
+      <c r="N87" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -6716,7 +6728,7 @@
         <v>12</v>
       </c>
       <c r="U87" t="n">
-        <v>1.054809641232527</v>
+        <v>1.054809641232528</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -6761,10 +6773,10 @@
       <c r="L88" t="n">
         <v>7.2</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="M88" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
-      <c r="N88" s="1" t="n">
+      <c r="N88" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -6833,10 +6845,10 @@
       <c r="L89" t="n">
         <v>7.2</v>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="M89" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
-      <c r="N89" s="1" t="n">
+      <c r="N89" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -6860,7 +6872,7 @@
         <v>21</v>
       </c>
       <c r="U89" t="n">
-        <v>0.05909630724279032</v>
+        <v>0.05909630724279033</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -6905,10 +6917,10 @@
       <c r="L90" t="n">
         <v>2.7</v>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="M90" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
-      <c r="N90" s="1" t="n">
+      <c r="N90" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -6977,10 +6989,10 @@
       <c r="L91" t="n">
         <v>2.4</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="M91" s="2" t="n">
         <v>46135.3603125</v>
       </c>
-      <c r="N91" s="1" t="n">
+      <c r="N91" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -7049,10 +7061,10 @@
       <c r="L92" t="n">
         <v>2.4</v>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="M92" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
-      <c r="N92" s="1" t="n">
+      <c r="N92" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -7121,10 +7133,10 @@
       <c r="L93" t="n">
         <v>7</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="M93" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
-      <c r="N93" s="1" t="n">
+      <c r="N93" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -7148,7 +7160,7 @@
         <v>12</v>
       </c>
       <c r="U93" t="n">
-        <v>0.8932008092606375</v>
+        <v>0.8932008092606385</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -7193,10 +7205,10 @@
       <c r="L94" t="n">
         <v>7</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="M94" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
-      <c r="N94" s="1" t="n">
+      <c r="N94" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -7220,7 +7232,7 @@
         <v>12</v>
       </c>
       <c r="U94" t="n">
-        <v>0.9188639769630813</v>
+        <v>0.9188639769630824</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -7265,10 +7277,10 @@
       <c r="L95" t="n">
         <v>7</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="M95" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
-      <c r="N95" s="1" t="n">
+      <c r="N95" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -7292,7 +7304,7 @@
         <v>12</v>
       </c>
       <c r="U95" t="n">
-        <v>0.890280317864258</v>
+        <v>0.8902803178642592</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -7337,10 +7349,10 @@
       <c r="L96" t="n">
         <v>6.9</v>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="M96" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
-      <c r="N96" s="1" t="n">
+      <c r="N96" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -7364,7 +7376,7 @@
         <v>12</v>
       </c>
       <c r="U96" t="n">
-        <v>0.8820036954096234</v>
+        <v>0.8820036954096245</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -7409,10 +7421,10 @@
       <c r="L97" t="n">
         <v>6.9</v>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="M97" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
-      <c r="N97" s="1" t="n">
+      <c r="N97" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -7436,7 +7448,7 @@
         <v>12</v>
       </c>
       <c r="U97" t="n">
-        <v>0.9123139363655175</v>
+        <v>0.9123139363655186</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -7481,10 +7493,10 @@
       <c r="L98" t="n">
         <v>7</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="M98" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
-      <c r="N98" s="1" t="n">
+      <c r="N98" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -7508,7 +7520,7 @@
         <v>12</v>
       </c>
       <c r="U98" t="n">
-        <v>0.9470652183601906</v>
+        <v>0.9470652183601916</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -7553,10 +7565,10 @@
       <c r="L99" t="n">
         <v>2.6</v>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="M99" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
-      <c r="N99" s="1" t="n">
+      <c r="N99" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -7580,7 +7592,7 @@
         <v>12</v>
       </c>
       <c r="U99" t="n">
-        <v>1.033987182388718</v>
+        <v>1.033987182388719</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -7625,10 +7637,10 @@
       <c r="L100" t="n">
         <v>2.6</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="M100" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
-      <c r="N100" s="1" t="n">
+      <c r="N100" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -7652,7 +7664,7 @@
         <v>12</v>
       </c>
       <c r="U100" t="n">
-        <v>1.122921528658659</v>
+        <v>1.12292152865866</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -7697,10 +7709,10 @@
       <c r="L101" t="n">
         <v>2.6</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="M101" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
-      <c r="N101" s="1" t="n">
+      <c r="N101" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -7724,7 +7736,7 @@
         <v>12</v>
       </c>
       <c r="U101" t="n">
-        <v>1.117818626892854</v>
+        <v>1.117818626892855</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -7769,10 +7781,10 @@
       <c r="L102" t="n">
         <v>7.2</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="M102" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
-      <c r="N102" s="1" t="n">
+      <c r="N102" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -7796,7 +7808,7 @@
         <v>12</v>
       </c>
       <c r="U102" t="n">
-        <v>1.091539604696913</v>
+        <v>1.091539604696914</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -7841,10 +7853,10 @@
       <c r="L103" t="n">
         <v>7</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="M103" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
-      <c r="N103" s="1" t="n">
+      <c r="N103" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -7868,7 +7880,7 @@
         <v>12</v>
       </c>
       <c r="U103" t="n">
-        <v>1.05591116631687</v>
+        <v>1.055911166316871</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -7913,10 +7925,10 @@
       <c r="L104" t="n">
         <v>7</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="M104" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
-      <c r="N104" s="1" t="n">
+      <c r="N104" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -7940,7 +7952,7 @@
         <v>12</v>
       </c>
       <c r="U104" t="n">
-        <v>1.007322027070148</v>
+        <v>1.007322027070149</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -7985,10 +7997,10 @@
       <c r="L105" t="n">
         <v>6.9</v>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="M105" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
-      <c r="N105" s="1" t="n">
+      <c r="N105" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -8057,10 +8069,10 @@
       <c r="L106" t="n">
         <v>6.9</v>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="M106" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
-      <c r="N106" s="1" t="n">
+      <c r="N106" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -8084,7 +8096,7 @@
         <v>12</v>
       </c>
       <c r="U106" t="n">
-        <v>0.9230940955909311</v>
+        <v>0.9230940955909321</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -8129,10 +8141,10 @@
       <c r="L107" t="n">
         <v>6.9</v>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="M107" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
-      <c r="N107" s="1" t="n">
+      <c r="N107" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -8156,7 +8168,7 @@
         <v>12</v>
       </c>
       <c r="U107" t="n">
-        <v>0.8445444094239999</v>
+        <v>0.8445444094240008</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -8201,10 +8213,10 @@
       <c r="L108" t="n">
         <v>6.9</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="M108" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
-      <c r="N108" s="1" t="n">
+      <c r="N108" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -8228,7 +8240,7 @@
         <v>12</v>
       </c>
       <c r="U108" t="n">
-        <v>0.8379330490779429</v>
+        <v>0.8379330490779437</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -8273,10 +8285,10 @@
       <c r="L109" t="n">
         <v>6.9</v>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="M109" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
-      <c r="N109" s="1" t="n">
+      <c r="N109" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -8300,7 +8312,7 @@
         <v>12</v>
       </c>
       <c r="U109" t="n">
-        <v>0.8501500688420979</v>
+        <v>0.8501500688420989</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -8345,10 +8357,10 @@
       <c r="L110" t="n">
         <v>6.9</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="M110" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
-      <c r="N110" s="1" t="n">
+      <c r="N110" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -8372,7 +8384,7 @@
         <v>12</v>
       </c>
       <c r="U110" t="n">
-        <v>0.8747942663565784</v>
+        <v>0.8747942663565793</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -8417,10 +8429,10 @@
       <c r="L111" t="n">
         <v>7</v>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="M111" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
-      <c r="N111" s="1" t="n">
+      <c r="N111" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -8444,7 +8456,7 @@
         <v>12</v>
       </c>
       <c r="U111" t="n">
-        <v>0.9397335161381659</v>
+        <v>0.9397335161381667</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -8489,10 +8501,10 @@
       <c r="L112" t="n">
         <v>7</v>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="M112" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
-      <c r="N112" s="1" t="n">
+      <c r="N112" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -8516,7 +8528,7 @@
         <v>12</v>
       </c>
       <c r="U112" t="n">
-        <v>0.9738869609860115</v>
+        <v>0.9738869609860124</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -8561,10 +8573,10 @@
       <c r="L113" t="n">
         <v>7.1</v>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="M113" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
-      <c r="N113" s="1" t="n">
+      <c r="N113" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -8588,7 +8600,7 @@
         <v>12</v>
       </c>
       <c r="U113" t="n">
-        <v>0.9370669472539528</v>
+        <v>0.9370669472539537</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -8633,10 +8645,10 @@
       <c r="L114" t="n">
         <v>2.4</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="M114" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
-      <c r="N114" s="1" t="n">
+      <c r="N114" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -8660,7 +8672,7 @@
         <v>12</v>
       </c>
       <c r="U114" t="n">
-        <v>0.965876844215081</v>
+        <v>0.9658768442150818</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -8705,10 +8717,10 @@
       <c r="L115" t="n">
         <v>2.4</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="M115" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
-      <c r="N115" s="1" t="n">
+      <c r="N115" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -8732,7 +8744,7 @@
         <v>12</v>
       </c>
       <c r="U115" t="n">
-        <v>0.9709005298561646</v>
+        <v>0.9709005298561655</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -8777,10 +8789,10 @@
       <c r="L116" t="n">
         <v>2.3</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="M116" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
-      <c r="N116" s="1" t="n">
+      <c r="N116" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -8804,7 +8816,7 @@
         <v>12</v>
       </c>
       <c r="U116" t="n">
-        <v>0.991877059379382</v>
+        <v>0.9918770593793829</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -8849,10 +8861,10 @@
       <c r="L117" t="n">
         <v>7.2</v>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="M117" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
-      <c r="N117" s="1" t="n">
+      <c r="N117" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -8876,7 +8888,7 @@
         <v>12</v>
       </c>
       <c r="U117" t="n">
-        <v>1.050153196747023</v>
+        <v>1.050153196747024</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -8921,10 +8933,10 @@
       <c r="L118" t="n">
         <v>7.3</v>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="M118" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
-      <c r="N118" s="1" t="n">
+      <c r="N118" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -8948,7 +8960,7 @@
         <v>12</v>
       </c>
       <c r="U118" t="n">
-        <v>1.105638323972259</v>
+        <v>1.10563832397226</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -8993,10 +9005,10 @@
       <c r="L119" t="n">
         <v>7.6</v>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="M119" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
-      <c r="N119" s="1" t="n">
+      <c r="N119" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -9020,7 +9032,7 @@
         <v>12</v>
       </c>
       <c r="U119" t="n">
-        <v>1.068466146494737</v>
+        <v>1.068466146494738</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -9065,10 +9077,10 @@
       <c r="L120" t="n">
         <v>7.4</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="M120" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
-      <c r="N120" s="1" t="n">
+      <c r="N120" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -9092,7 +9104,7 @@
         <v>12</v>
       </c>
       <c r="U120" t="n">
-        <v>1.088071453981714</v>
+        <v>1.088071453981715</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -9137,10 +9149,10 @@
       <c r="L121" t="n">
         <v>7.1</v>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="M121" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
-      <c r="N121" s="1" t="n">
+      <c r="N121" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O121" t="inlineStr">
@@ -9164,7 +9176,7 @@
         <v>12</v>
       </c>
       <c r="U121" t="n">
-        <v>1.090363373116287</v>
+        <v>1.090363373116288</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -9209,10 +9221,10 @@
       <c r="L122" t="n">
         <v>7.2</v>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="M122" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
-      <c r="N122" s="1" t="n">
+      <c r="N122" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O122" t="inlineStr">
@@ -9236,7 +9248,7 @@
         <v>12</v>
       </c>
       <c r="U122" t="n">
-        <v>1.085382425265535</v>
+        <v>1.085382425265536</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -9281,10 +9293,10 @@
       <c r="L123" t="n">
         <v>2.5</v>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="M123" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
-      <c r="N123" s="1" t="n">
+      <c r="N123" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O123" t="inlineStr">
@@ -9353,10 +9365,10 @@
       <c r="L124" t="n">
         <v>2.5</v>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="M124" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
-      <c r="N124" s="1" t="n">
+      <c r="N124" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="O124" t="inlineStr">
@@ -9380,7 +9392,7 @@
         <v>12</v>
       </c>
       <c r="U124" t="n">
-        <v>1.785398160172424</v>
+        <v>1.785398160172425</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -9425,10 +9437,10 @@
       <c r="L125" t="n">
         <v>2.5</v>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="M125" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
-      <c r="N125" s="1" t="n">
+      <c r="N125" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O125" t="inlineStr">
@@ -9452,7 +9464,7 @@
         <v>12</v>
       </c>
       <c r="U125" t="n">
-        <v>1.773218147454992</v>
+        <v>1.773218147454993</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -9497,10 +9509,10 @@
       <c r="L126" t="n">
         <v>7</v>
       </c>
-      <c r="M126" s="1" t="n">
+      <c r="M126" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
-      <c r="N126" s="1" t="n">
+      <c r="N126" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O126" t="inlineStr">
@@ -9569,10 +9581,10 @@
       <c r="L127" t="n">
         <v>6.7</v>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="M127" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
-      <c r="N127" s="1" t="n">
+      <c r="N127" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O127" t="inlineStr">
@@ -9641,10 +9653,10 @@
       <c r="L128" t="n">
         <v>6.7</v>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="M128" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
-      <c r="N128" s="1" t="n">
+      <c r="N128" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O128" t="inlineStr">
@@ -9668,7 +9680,7 @@
         <v>12</v>
       </c>
       <c r="U128" t="n">
-        <v>1.131389665665405</v>
+        <v>1.131389665665406</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -9713,10 +9725,10 @@
       <c r="L129" t="n">
         <v>7</v>
       </c>
-      <c r="M129" s="1" t="n">
+      <c r="M129" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
-      <c r="N129" s="1" t="n">
+      <c r="N129" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O129" t="inlineStr">
@@ -9785,10 +9797,10 @@
       <c r="L130" t="n">
         <v>7.7</v>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="M130" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
-      <c r="N130" s="1" t="n">
+      <c r="N130" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="O130" t="inlineStr">
@@ -9857,10 +9869,10 @@
       <c r="L131" t="n">
         <v>7.7</v>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="M131" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
-      <c r="N131" s="1" t="n">
+      <c r="N131" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O131" t="inlineStr">
@@ -9884,7 +9896,7 @@
         <v>12</v>
       </c>
       <c r="U131" t="n">
-        <v>1.143806599475458</v>
+        <v>1.143806599475459</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -9929,10 +9941,10 @@
       <c r="L132" t="n">
         <v>7.7</v>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="M132" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
-      <c r="N132" s="1" t="n">
+      <c r="N132" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O132" t="inlineStr">
@@ -9956,7 +9968,7 @@
         <v>12</v>
       </c>
       <c r="U132" t="n">
-        <v>1.170156032278075</v>
+        <v>1.170156032278076</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -10001,10 +10013,10 @@
       <c r="L133" t="n">
         <v>7.4</v>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="M133" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
-      <c r="N133" s="1" t="n">
+      <c r="N133" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O133" t="inlineStr">
@@ -10028,7 +10040,7 @@
         <v>12</v>
       </c>
       <c r="U133" t="n">
-        <v>1.178880614367892</v>
+        <v>1.178880614367893</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -10073,10 +10085,10 @@
       <c r="L134" t="n">
         <v>7.5</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="M134" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
-      <c r="N134" s="1" t="n">
+      <c r="N134" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O134" t="inlineStr">
@@ -10100,7 +10112,7 @@
         <v>12</v>
       </c>
       <c r="U134" t="n">
-        <v>1.189182291143884</v>
+        <v>1.189182291143885</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -10145,10 +10157,10 @@
       <c r="L135" t="n">
         <v>7.9</v>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="M135" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
-      <c r="N135" s="1" t="n">
+      <c r="N135" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O135" t="inlineStr">
@@ -10172,7 +10184,7 @@
         <v>12</v>
       </c>
       <c r="U135" t="n">
-        <v>1.195478327948276</v>
+        <v>1.195478327948277</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -10217,10 +10229,10 @@
       <c r="L136" t="n">
         <v>7.9</v>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="M136" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
-      <c r="N136" s="1" t="n">
+      <c r="N136" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="O136" t="inlineStr">
@@ -10244,7 +10256,7 @@
         <v>12</v>
       </c>
       <c r="U136" t="n">
-        <v>1.19873414482643</v>
+        <v>1.198734144826431</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -10289,10 +10301,10 @@
       <c r="L137" t="n">
         <v>7.9</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="M137" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
-      <c r="N137" s="1" t="n">
+      <c r="N137" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O137" t="inlineStr">
@@ -10316,7 +10328,7 @@
         <v>12</v>
       </c>
       <c r="U137" t="n">
-        <v>1.154820480261311</v>
+        <v>1.154820480261312</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -10361,10 +10373,10 @@
       <c r="L138" t="n">
         <v>2.5</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="M138" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
-      <c r="N138" s="1" t="n">
+      <c r="N138" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O138" t="inlineStr">
@@ -10388,7 +10400,7 @@
         <v>12</v>
       </c>
       <c r="U138" t="n">
-        <v>1.138534805759957</v>
+        <v>1.138534805759958</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -10433,10 +10445,10 @@
       <c r="L139" t="n">
         <v>2.5</v>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="M139" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
-      <c r="N139" s="1" t="n">
+      <c r="N139" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O139" t="inlineStr">
@@ -10460,7 +10472,7 @@
         <v>12</v>
       </c>
       <c r="U139" t="n">
-        <v>1.147034755880734</v>
+        <v>1.147034755880735</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -10505,10 +10517,10 @@
       <c r="L140" t="n">
         <v>2.5</v>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="M140" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
-      <c r="N140" s="1" t="n">
+      <c r="N140" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O140" t="inlineStr">
@@ -10532,7 +10544,7 @@
         <v>12</v>
       </c>
       <c r="U140" t="n">
-        <v>1.122151189798379</v>
+        <v>1.12215118979838</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -10577,10 +10589,10 @@
       <c r="L141" t="n">
         <v>7.9</v>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="M141" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
-      <c r="N141" s="1" t="n">
+      <c r="N141" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O141" t="inlineStr">
@@ -10604,7 +10616,7 @@
         <v>12</v>
       </c>
       <c r="U141" t="n">
-        <v>1.102212159703974</v>
+        <v>1.102212159703975</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -10649,10 +10661,10 @@
       <c r="L142" t="n">
         <v>7.9</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="M142" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
-      <c r="N142" s="1" t="n">
+      <c r="N142" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="O142" t="inlineStr">
@@ -10676,7 +10688,7 @@
         <v>12</v>
       </c>
       <c r="U142" t="n">
-        <v>1.064584617984975</v>
+        <v>1.064584617984976</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -10721,10 +10733,10 @@
       <c r="L143" t="n">
         <v>7.9</v>
       </c>
-      <c r="M143" s="1" t="n">
+      <c r="M143" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
-      <c r="N143" s="1" t="n">
+      <c r="N143" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O143" t="inlineStr">
@@ -10748,7 +10760,7 @@
         <v>12</v>
       </c>
       <c r="U143" t="n">
-        <v>1.025957418485618</v>
+        <v>1.025957418485619</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -10793,10 +10805,10 @@
       <c r="L144" t="n">
         <v>7.7</v>
       </c>
-      <c r="M144" s="1" t="n">
+      <c r="M144" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
-      <c r="N144" s="1" t="n">
+      <c r="N144" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O144" t="inlineStr">
@@ -10820,7 +10832,7 @@
         <v>12</v>
       </c>
       <c r="U144" t="n">
-        <v>0.9890651163468485</v>
+        <v>0.9890651163468493</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -10865,10 +10877,10 @@
       <c r="L145" t="n">
         <v>7.4</v>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="M145" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
-      <c r="N145" s="1" t="n">
+      <c r="N145" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O145" t="inlineStr">
@@ -10892,7 +10904,7 @@
         <v>12</v>
       </c>
       <c r="U145" t="n">
-        <v>1.013252346516917</v>
+        <v>1.013252346516918</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -10937,10 +10949,10 @@
       <c r="L146" t="n">
         <v>7.6</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="M146" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
-      <c r="N146" s="1" t="n">
+      <c r="N146" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O146" t="inlineStr">
@@ -10964,7 +10976,7 @@
         <v>12</v>
       </c>
       <c r="U146" t="n">
-        <v>1.036636099458925</v>
+        <v>1.036636099458926</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -11009,10 +11021,10 @@
       <c r="L147" t="n">
         <v>2.5</v>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="M147" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
-      <c r="N147" s="1" t="n">
+      <c r="N147" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O147" t="inlineStr">
@@ -11036,7 +11048,7 @@
         <v>12</v>
       </c>
       <c r="U147" t="n">
-        <v>1.093139496605096</v>
+        <v>1.093139496605097</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -11081,10 +11093,10 @@
       <c r="L148" t="n">
         <v>2.5</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="M148" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
-      <c r="N148" s="1" t="n">
+      <c r="N148" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="O148" t="inlineStr">
@@ -11153,10 +11165,10 @@
       <c r="L149" t="n">
         <v>2.4</v>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="M149" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
-      <c r="N149" s="1" t="n">
+      <c r="N149" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O149" t="inlineStr">
@@ -11180,7 +11192,7 @@
         <v>12</v>
       </c>
       <c r="U149" t="n">
-        <v>0.9996391264285803</v>
+        <v>0.9996391264285812</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -11225,10 +11237,10 @@
       <c r="L150" t="n">
         <v>7.8</v>
       </c>
-      <c r="M150" s="1" t="n">
+      <c r="M150" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
-      <c r="N150" s="1" t="n">
+      <c r="N150" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O150" t="inlineStr">
@@ -11252,7 +11264,7 @@
         <v>12</v>
       </c>
       <c r="U150" t="n">
-        <v>1.013282742787104</v>
+        <v>1.013282742787105</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -11297,10 +11309,10 @@
       <c r="L151" t="n">
         <v>7.2</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="M151" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
-      <c r="N151" s="1" t="n">
+      <c r="N151" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O151" t="inlineStr">
@@ -11324,7 +11336,7 @@
         <v>12</v>
       </c>
       <c r="U151" t="n">
-        <v>1.500044215714579</v>
+        <v>1.50004421571458</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -11369,10 +11381,10 @@
       <c r="L152" t="n">
         <v>7.2</v>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="M152" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
-      <c r="N152" s="1" t="n">
+      <c r="N152" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O152" t="inlineStr">
@@ -11396,7 +11408,7 @@
         <v>12</v>
       </c>
       <c r="U152" t="n">
-        <v>1.492466424705045</v>
+        <v>1.492466424705046</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -11441,10 +11453,10 @@
       <c r="L153" t="n">
         <v>7.6</v>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="M153" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
-      <c r="N153" s="1" t="n">
+      <c r="N153" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O153" t="inlineStr">
@@ -11468,7 +11480,7 @@
         <v>12</v>
       </c>
       <c r="U153" t="n">
-        <v>1.535433910218675</v>
+        <v>1.535433910218676</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
@@ -11513,10 +11525,10 @@
       <c r="L154" t="n">
         <v>7.5</v>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="M154" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
-      <c r="N154" s="1" t="n">
+      <c r="N154" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="O154" t="inlineStr">
